--- a/data/ZERGY (TRY).xlsx
+++ b/data/ZERGY (TRY).xlsx
@@ -403,12 +403,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:G108"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
+    <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -416,12 +419,21 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="G1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -435,13 +447,22 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerleri</v>
       </c>
       <c r="B3">
-        <v>101213270</v>
+        <v>1814718</v>
       </c>
       <c r="C3">
-        <v>3461439</v>
+        <v>5396258.85265883</v>
       </c>
       <c r="D3">
-        <v>81354499</v>
+        <v>13081335</v>
+      </c>
+      <c r="E3">
+        <v>124379585.03783537</v>
+      </c>
+      <c r="F3">
+        <v>4253715.072125606</v>
+      </c>
+      <c r="G3">
+        <v>99975416.52968028</v>
       </c>
     </row>
     <row r="4">
@@ -454,13 +475,22 @@
         <v xml:space="preserve">    Finansal Yatırımlar</v>
       </c>
       <c r="B5">
-        <v>12182</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>15280</v>
+        <v>290185765.54614747</v>
       </c>
       <c r="D5">
-        <v>31826</v>
+        <v>1063632690</v>
+      </c>
+      <c r="E5">
+        <v>14970.290999697081</v>
+      </c>
+      <c r="F5">
+        <v>18777.994570089388</v>
+      </c>
+      <c r="G5">
+        <v>39110.530401933946</v>
       </c>
     </row>
     <row r="6">
@@ -473,10 +503,19 @@
         <v xml:space="preserve">    Ticari Alacaklar</v>
       </c>
       <c r="B7">
-        <v>676629466</v>
+        <v>306000221</v>
       </c>
       <c r="C7">
-        <v>528867294</v>
+        <v>561548156.2891066</v>
+      </c>
+      <c r="D7">
+        <v>649024893</v>
+      </c>
+      <c r="E7">
+        <v>831500575.0278808</v>
+      </c>
+      <c r="F7">
+        <v>649917688.778552</v>
       </c>
     </row>
     <row r="8">
@@ -494,10 +533,19 @@
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
       <c r="B10">
-        <v>19961218</v>
+        <v>21332489</v>
       </c>
       <c r="C10">
-        <v>198432774</v>
+        <v>21378558.40316908</v>
+      </c>
+      <c r="D10">
+        <v>23506312</v>
+      </c>
+      <c r="E10">
+        <v>24530064.20689471</v>
+      </c>
+      <c r="F10">
+        <v>243851285.96058196</v>
       </c>
     </row>
     <row r="11">
@@ -520,19 +568,28 @@
         <v xml:space="preserve">    Stoklar</v>
       </c>
       <c r="B14">
-        <v>3057400447</v>
-      </c>
-      <c r="C14">
-        <v>2649715704</v>
+        <v>6433032321</v>
       </c>
       <c r="D14">
-        <v>2879588850</v>
+        <v>6102524506</v>
+      </c>
+      <c r="E14">
+        <v>3757197044.343616</v>
+      </c>
+      <c r="G14">
+        <v>3538686836.6428394</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v xml:space="preserve">    Proje Halindeki Stoklar</v>
       </c>
+      <c r="C15">
+        <v>6328799954.084393</v>
+      </c>
+      <c r="F15">
+        <v>3256198912.688139</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -544,13 +601,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderler</v>
       </c>
       <c r="B17">
-        <v>2088654332</v>
+        <v>1680446822</v>
       </c>
       <c r="C17">
-        <v>1238760091</v>
+        <v>1262723145.0335245</v>
       </c>
       <c r="D17">
-        <v>674622924</v>
+        <v>470143075</v>
+      </c>
+      <c r="E17">
+        <v>2566718367.084052</v>
+      </c>
+      <c r="F17">
+        <v>1522295110.3098893</v>
+      </c>
+      <c r="G17">
+        <v>829034763.3677992</v>
       </c>
     </row>
     <row r="18">
@@ -562,11 +628,20 @@
       <c r="A19" t="str">
         <v xml:space="preserve">    Cari Dönem Vergisiyle İlgili Varlıklar</v>
       </c>
+      <c r="B19">
+        <v>740879</v>
+      </c>
       <c r="C19">
-        <v>65205</v>
+        <v>13676062.296503</v>
       </c>
       <c r="D19">
-        <v>199864</v>
+        <v>14694638</v>
+      </c>
+      <c r="F19">
+        <v>80127.37266603489</v>
+      </c>
+      <c r="G19">
+        <v>245610.1001775946</v>
       </c>
     </row>
     <row r="20">
@@ -579,13 +654,22 @@
         <v xml:space="preserve">    Diğer Dönen Varlıklar</v>
       </c>
       <c r="B21">
-        <v>412226904</v>
+        <v>750369281</v>
       </c>
       <c r="C21">
-        <v>446733291</v>
+        <v>801768172.5596317</v>
       </c>
       <c r="D21">
-        <v>603053443</v>
+        <v>876507940</v>
+      </c>
+      <c r="E21">
+        <v>506579930.2892951</v>
+      </c>
+      <c r="F21">
+        <v>548984351.1208156</v>
+      </c>
+      <c r="G21">
+        <v>741084019.8718796</v>
       </c>
     </row>
     <row r="22">
@@ -603,13 +687,22 @@
         <v xml:space="preserve">    Toplam Dönen Varlıklar</v>
       </c>
       <c r="B24">
-        <v>6356097819</v>
+        <v>9193736731</v>
       </c>
       <c r="C24">
-        <v>5066051078</v>
+        <v>9285476073.065134</v>
       </c>
       <c r="D24">
-        <v>4238851406</v>
+        <v>9213115389</v>
+      </c>
+      <c r="E24">
+        <v>7810920536.280575</v>
+      </c>
+      <c r="F24">
+        <v>6225599969.29734</v>
+      </c>
+      <c r="G24">
+        <v>5209065757.042777</v>
       </c>
     </row>
     <row r="25">
@@ -641,11 +734,14 @@
       <c r="A30" t="str">
         <v xml:space="preserve">    Diğer Alacaklar</v>
       </c>
-      <c r="B30">
-        <v>680866</v>
-      </c>
       <c r="C30">
-        <v>854007</v>
+        <v>728617.8660525405</v>
+      </c>
+      <c r="E30">
+        <v>836706.7929568012</v>
+      </c>
+      <c r="F30">
+        <v>1049477.4575980331</v>
       </c>
     </row>
     <row r="31">
@@ -667,6 +763,18 @@
       <c r="A34" t="str">
         <v xml:space="preserve">    Stoklar</v>
       </c>
+      <c r="B34">
+        <v>1923770729</v>
+      </c>
+      <c r="C34">
+        <v>1907254410.0882452</v>
+      </c>
+      <c r="D34">
+        <v>1873296835</v>
+      </c>
+      <c r="F34">
+        <v>941338506.712471</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -693,7 +801,19 @@
         <v xml:space="preserve">    Maddi Duran Varlıklar</v>
       </c>
       <c r="B39">
-        <v>7367657</v>
+        <v>6771779</v>
+      </c>
+      <c r="C39">
+        <v>7172464.079855383</v>
+      </c>
+      <c r="D39">
+        <v>7573148</v>
+      </c>
+      <c r="E39">
+        <v>9054011.597106813</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -731,13 +851,16 @@
         <v xml:space="preserve">    Diğer Duran Varlıklar</v>
       </c>
       <c r="B46">
-        <v>809388001</v>
-      </c>
-      <c r="C46">
-        <v>766009538</v>
+        <v>680866</v>
       </c>
       <c r="D46">
-        <v>560621253</v>
+        <v>801787</v>
+      </c>
+      <c r="E46">
+        <v>994645699.1161642</v>
+      </c>
+      <c r="G46">
+        <v>688939689.5439829</v>
       </c>
     </row>
     <row r="47">
@@ -745,13 +868,22 @@
         <v xml:space="preserve">    Toplam Duran Varlıklar</v>
       </c>
       <c r="B47">
-        <v>817436524</v>
+        <v>1931223374</v>
       </c>
       <c r="C47">
-        <v>766863545</v>
+        <v>1915155492.034153</v>
       </c>
       <c r="D47">
-        <v>560621253</v>
+        <v>1881671770</v>
+      </c>
+      <c r="E47">
+        <v>1004536417.5062279</v>
+      </c>
+      <c r="F47">
+        <v>942387984.170069</v>
+      </c>
+      <c r="G47">
+        <v>688939689.5439829</v>
       </c>
     </row>
     <row r="48">
@@ -759,13 +891,22 @@
         <v xml:space="preserve">    Toplam Varlıklar</v>
       </c>
       <c r="B48">
-        <v>7173534343</v>
+        <v>11124960105</v>
       </c>
       <c r="C48">
-        <v>5832914623</v>
+        <v>11200631565.099287</v>
       </c>
       <c r="D48">
-        <v>4799472659</v>
+        <v>11094787159</v>
+      </c>
+      <c r="E48">
+        <v>8815456953.7868</v>
+      </c>
+      <c r="F48">
+        <v>7167987953.467408</v>
+      </c>
+      <c r="G48">
+        <v>5898005446.5867605</v>
       </c>
     </row>
     <row r="49">
@@ -778,10 +919,19 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B50">
-        <v>338182267</v>
+        <v>480150328</v>
       </c>
       <c r="C50">
-        <v>303284967</v>
+        <v>370925734.29952884</v>
+      </c>
+      <c r="D50">
+        <v>336201928</v>
+      </c>
+      <c r="E50">
+        <v>415587501.88206005</v>
+      </c>
+      <c r="F50">
+        <v>372702693.40708965</v>
       </c>
     </row>
     <row r="51">
@@ -794,13 +944,22 @@
         <v xml:space="preserve">    Ticari Borçlar</v>
       </c>
       <c r="B52">
-        <v>15576480</v>
+        <v>467972591</v>
       </c>
       <c r="C52">
-        <v>2866636</v>
+        <v>510330806.09337586</v>
       </c>
       <c r="D52">
-        <v>636106</v>
+        <v>607864809</v>
+      </c>
+      <c r="E52">
+        <v>19141720.435967952</v>
+      </c>
+      <c r="F52">
+        <v>3522768.7387751974</v>
+      </c>
+      <c r="G52">
+        <v>781701.8491752842</v>
       </c>
     </row>
     <row r="53">
@@ -813,21 +972,30 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlar</v>
       </c>
       <c r="B54">
-        <v>1753307</v>
+        <v>934015</v>
       </c>
       <c r="C54">
-        <v>2308379</v>
+        <v>2861976.0401190673</v>
       </c>
       <c r="D54">
-        <v>559094</v>
+        <v>2975156</v>
+      </c>
+      <c r="E54">
+        <v>2154614.677541117</v>
+      </c>
+      <c r="F54">
+        <v>2836733.6782777966</v>
+      </c>
+      <c r="G54">
+        <v>687062.8694947168</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
         <v xml:space="preserve">    Diğer Borçlar</v>
       </c>
-      <c r="D55">
-        <v>424494</v>
+      <c r="G55">
+        <v>521654.7945842565</v>
       </c>
     </row>
     <row r="56">
@@ -835,13 +1003,22 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
       </c>
       <c r="B56">
-        <v>2841287968</v>
+        <v>3487027721</v>
       </c>
       <c r="C56">
-        <v>2315423118</v>
+        <v>3424575236.0216494</v>
       </c>
       <c r="D56">
-        <v>2203313138</v>
+        <v>3390039893</v>
+      </c>
+      <c r="E56">
+        <v>3491619413.470531</v>
+      </c>
+      <c r="F56">
+        <v>2845391385.3705664</v>
+      </c>
+      <c r="G56">
+        <v>2707620985.0037546</v>
       </c>
     </row>
     <row r="57">
@@ -868,8 +1045,8 @@
       <c r="A61" t="str">
         <v xml:space="preserve">    Dönem Karı Vergi Yükümlülüğü</v>
       </c>
-      <c r="B61">
-        <v>11170555</v>
+      <c r="E61">
+        <v>13727340.25431959</v>
       </c>
     </row>
     <row r="62">
@@ -877,10 +1054,19 @@
         <v xml:space="preserve">    Kısa Vadeli Karşılıklar</v>
       </c>
       <c r="B62">
-        <v>7960500</v>
+        <v>6558263</v>
       </c>
       <c r="C62">
-        <v>1063882</v>
+        <v>8934059.837483255</v>
+      </c>
+      <c r="D62">
+        <v>7970890</v>
+      </c>
+      <c r="E62">
+        <v>9782548.145057347</v>
+      </c>
+      <c r="F62">
+        <v>1307390.4927643882</v>
       </c>
     </row>
     <row r="63">
@@ -888,13 +1074,22 @@
         <v xml:space="preserve">    Diğer Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B63">
-        <v>36774039</v>
+        <v>249695928</v>
       </c>
       <c r="C63">
-        <v>169487298</v>
+        <v>288708429.48684424</v>
       </c>
       <c r="D63">
-        <v>103522</v>
+        <v>314856696</v>
+      </c>
+      <c r="E63">
+        <v>45191106.96636098</v>
+      </c>
+      <c r="F63">
+        <v>208280593.4073714</v>
+      </c>
+      <c r="G63">
+        <v>127216.75134383855</v>
       </c>
     </row>
     <row r="64">
@@ -912,13 +1107,22 @@
         <v xml:space="preserve">    Toplam Kısa Vadeli Yükümlülükler</v>
       </c>
       <c r="B66">
-        <v>3252705116</v>
+        <v>4692338846</v>
       </c>
       <c r="C66">
-        <v>2794434280</v>
+        <v>4606336241.779</v>
       </c>
       <c r="D66">
-        <v>2205036354</v>
+        <v>4659909372</v>
+      </c>
+      <c r="E66">
+        <v>3997204245.831838</v>
+      </c>
+      <c r="F66">
+        <v>3434041565.0948443</v>
+      </c>
+      <c r="G66">
+        <v>2709738621.268352</v>
       </c>
     </row>
     <row r="67">
@@ -931,10 +1135,19 @@
         <v xml:space="preserve">    Finansal Borçlar</v>
       </c>
       <c r="B68">
-        <v>552171068</v>
+        <v>612731427</v>
       </c>
       <c r="C68">
-        <v>62676770</v>
+        <v>690536481.5160937</v>
+      </c>
+      <c r="D68">
+        <v>763174363</v>
+      </c>
+      <c r="E68">
+        <v>678555374.2877628</v>
+      </c>
+      <c r="F68">
+        <v>77022613.90948442</v>
       </c>
     </row>
     <row r="69">
@@ -967,13 +1180,22 @@
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülükler</v>
       </c>
       <c r="B74">
-        <v>2263876239</v>
+        <v>2804964032</v>
       </c>
       <c r="C74">
-        <v>2011178762</v>
+        <v>2783466123.6389184</v>
       </c>
       <c r="D74">
-        <v>1803380875</v>
+        <v>2738115550</v>
+      </c>
+      <c r="E74">
+        <v>2782046140.6279573</v>
+      </c>
+      <c r="F74">
+        <v>2471509712.7599316</v>
+      </c>
+      <c r="G74">
+        <v>2216149768.678242</v>
       </c>
     </row>
     <row r="75">
@@ -1006,7 +1228,19 @@
         <v xml:space="preserve">    Uzun vadeli Karşılıklar</v>
       </c>
       <c r="B80">
-        <v>1679248</v>
+        <v>1174149</v>
+      </c>
+      <c r="C80">
+        <v>1388640.141762829</v>
+      </c>
+      <c r="D80">
+        <v>1799070</v>
+      </c>
+      <c r="E80">
+        <v>2063604.5986422037</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -1019,13 +1253,22 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Yükümlülüğü</v>
       </c>
       <c r="B82">
-        <v>175322195</v>
+        <v>22528962</v>
       </c>
       <c r="C82">
-        <v>114381616</v>
+        <v>79963644.31295356</v>
       </c>
       <c r="D82">
-        <v>81381170</v>
+        <v>89962802</v>
+      </c>
+      <c r="E82">
+        <v>215451016.07746157</v>
+      </c>
+      <c r="F82">
+        <v>140561982.39336118</v>
+      </c>
+      <c r="G82">
+        <v>100008192.15201266</v>
       </c>
     </row>
     <row r="83">
@@ -1038,13 +1281,22 @@
         <v xml:space="preserve">    Toplam Uzun Vadeli Yükümlülükler</v>
       </c>
       <c r="B84">
-        <v>2993048750</v>
+        <v>3441398570</v>
       </c>
       <c r="C84">
-        <v>2188237148</v>
+        <v>3555354889.609729</v>
       </c>
       <c r="D84">
-        <v>1884762045</v>
+        <v>3593051785</v>
+      </c>
+      <c r="E84">
+        <v>3678116135.5918236</v>
+      </c>
+      <c r="F84">
+        <v>2689094309.062777</v>
+      </c>
+      <c r="G84">
+        <v>2316157960.830255</v>
       </c>
     </row>
     <row r="85">
@@ -1057,13 +1309,22 @@
         <v xml:space="preserve">    Ana Ortaklığa Ait Özkaynaklar</v>
       </c>
       <c r="B86">
-        <v>927780477</v>
+        <v>2991222689</v>
       </c>
       <c r="C86">
-        <v>850243195</v>
+        <v>3038940433.7105575</v>
       </c>
       <c r="D86">
-        <v>709674260</v>
+        <v>2841826002</v>
+      </c>
+      <c r="E86">
+        <v>1140136572.3631394</v>
+      </c>
+      <c r="F86">
+        <v>1044852079.3097868</v>
+      </c>
+      <c r="G86">
+        <v>872108864.4881536</v>
       </c>
     </row>
     <row r="87">
@@ -1071,12 +1332,21 @@
         <v xml:space="preserve">    Ödenmiş Sermaye</v>
       </c>
       <c r="B87">
+        <v>626000000</v>
+      </c>
+      <c r="C87">
+        <v>626000000</v>
+      </c>
+      <c r="D87">
+        <v>626000000</v>
+      </c>
+      <c r="E87">
         <v>510000000</v>
       </c>
-      <c r="C87">
+      <c r="F87">
         <v>510000000</v>
       </c>
-      <c r="D87">
+      <c r="G87">
         <v>250000000</v>
       </c>
     </row>
@@ -1085,13 +1355,22 @@
         <v xml:space="preserve">    Sermaye Düzeltme Farkları</v>
       </c>
       <c r="B88">
-        <v>407210754</v>
+        <v>637749075</v>
       </c>
       <c r="C88">
-        <v>407210754</v>
+        <v>637749076.092613</v>
       </c>
       <c r="D88">
-        <v>225946449</v>
+        <v>637749075</v>
+      </c>
+      <c r="E88">
+        <v>617147586.2281705</v>
+      </c>
+      <c r="F88">
+        <v>617147584.9476476</v>
+      </c>
+      <c r="G88">
+        <v>334883996.2077234</v>
       </c>
     </row>
     <row r="89">
@@ -1113,6 +1392,15 @@
       <c r="A92" t="str">
         <v xml:space="preserve">    Geri Alınmış Paylar (-)</v>
       </c>
+      <c r="B92">
+        <v>-1133378</v>
+      </c>
+      <c r="C92">
+        <v>-1133377.8648344602</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -1123,6 +1411,18 @@
       <c r="A94" t="str">
         <v xml:space="preserve">    Paylara İlişkin Primler (İskontolar)</v>
       </c>
+      <c r="B94">
+        <v>1593382759</v>
+      </c>
+      <c r="C94">
+        <v>1593382759.4884944</v>
+      </c>
+      <c r="D94">
+        <v>1593382759</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -1139,7 +1439,19 @@
         <v xml:space="preserve">    Kar veya Zararda Yeniden Sınıflandırılmayacak Birikmiş Diğer Kapsamlı Gelirler (Giderler)</v>
       </c>
       <c r="B97">
-        <v>-943976</v>
+        <v>-534881</v>
+      </c>
+      <c r="C97">
+        <v>-612489.0630453561</v>
+      </c>
+      <c r="D97">
+        <v>-946179</v>
+      </c>
+      <c r="E97">
+        <v>-1160039.026164017</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -1172,13 +1484,22 @@
         <v xml:space="preserve">    Geçmiş Yıllar Kar/Zararları</v>
       </c>
       <c r="B103">
-        <v>-66967559</v>
+        <v>-14359653</v>
       </c>
       <c r="C103">
-        <v>233727811</v>
+        <v>-14359649.99335099</v>
       </c>
       <c r="D103">
-        <v>99281031</v>
+        <v>-82295505</v>
+      </c>
+      <c r="E103">
+        <v>-82295505.31681031</v>
+      </c>
+      <c r="F103">
+        <v>287224867.6283585</v>
+      </c>
+      <c r="G103">
+        <v>122005083.3048717</v>
       </c>
     </row>
     <row r="104">
@@ -1186,13 +1507,22 @@
         <v xml:space="preserve">    Dönem Net Kar/Zararı</v>
       </c>
       <c r="B104">
-        <v>78481258</v>
+        <v>150118767</v>
       </c>
       <c r="C104">
-        <v>-300695370</v>
+        <v>197914115.05068097</v>
       </c>
       <c r="D104">
-        <v>134446780</v>
+        <v>67935852</v>
+      </c>
+      <c r="E104">
+        <v>96444530.47794324</v>
+      </c>
+      <c r="F104">
+        <v>-369520373.2662193</v>
+      </c>
+      <c r="G104">
+        <v>165219784.9755585</v>
       </c>
     </row>
     <row r="105">
@@ -1205,13 +1535,22 @@
         <v xml:space="preserve">    Toplam Özkaynaklar</v>
       </c>
       <c r="B106">
-        <v>927780477</v>
+        <v>2991222689</v>
       </c>
       <c r="C106">
-        <v>850243195</v>
+        <v>3038940433.7105575</v>
       </c>
       <c r="D106">
-        <v>709674260</v>
+        <v>2841826002</v>
+      </c>
+      <c r="E106">
+        <v>1140136572.3631394</v>
+      </c>
+      <c r="F106">
+        <v>1044852079.3097868</v>
+      </c>
+      <c r="G106">
+        <v>872108864.4881536</v>
       </c>
     </row>
     <row r="107">
@@ -1219,13 +1558,22 @@
         <v xml:space="preserve">    Toplam Kaynaklar</v>
       </c>
       <c r="B107">
-        <v>7173534343</v>
+        <v>11124960105</v>
       </c>
       <c r="C107">
-        <v>5832914623</v>
+        <v>11200631565.099287</v>
       </c>
       <c r="D107">
-        <v>4799472659</v>
+        <v>11094787159</v>
+      </c>
+      <c r="E107">
+        <v>8815456953.7868</v>
+      </c>
+      <c r="F107">
+        <v>7167987953.467408</v>
+      </c>
+      <c r="G107">
+        <v>5898005446.5867605</v>
       </c>
     </row>
     <row r="108">
@@ -1235,20 +1583,25 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G108"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:J50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1256,15 +1609,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -1278,13 +1646,28 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>255926958</v>
+        <v>22887332</v>
       </c>
       <c r="C3">
-        <v>2433120321</v>
+        <v>7953620</v>
       </c>
       <c r="D3">
-        <v>1549742795</v>
+        <v>391932632.8314423</v>
+      </c>
+      <c r="E3">
+        <v>314505092.42548454</v>
+      </c>
+      <c r="F3">
+        <v>33288289</v>
+      </c>
+      <c r="G3">
+        <v>33288289</v>
+      </c>
+      <c r="H3">
+        <v>2990027847.549113</v>
+      </c>
+      <c r="I3">
+        <v>1904457446.711041</v>
       </c>
     </row>
     <row r="4">
@@ -1307,13 +1690,28 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-125150104</v>
+        <v>-17800387</v>
       </c>
       <c r="C7">
-        <v>-2371579071</v>
+        <v>-3411098</v>
       </c>
       <c r="D7">
-        <v>-1510203613</v>
+        <v>-190704972.2237021</v>
+      </c>
+      <c r="E7">
+        <v>-153795228.65886992</v>
+      </c>
+      <c r="F7">
+        <v>-15915545</v>
+      </c>
+      <c r="G7">
+        <v>-15915545</v>
+      </c>
+      <c r="H7">
+        <v>-2914400659.08273</v>
+      </c>
+      <c r="I7">
+        <v>-1855868293.8272789</v>
       </c>
     </row>
     <row r="8">
@@ -1321,13 +1719,28 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>130776854</v>
+        <v>5086945</v>
       </c>
       <c r="C8">
-        <v>61541250</v>
+        <v>4542522</v>
       </c>
       <c r="D8">
-        <v>39539182</v>
+        <v>201227660.6077402</v>
+      </c>
+      <c r="E8">
+        <v>160709863.7666146</v>
+      </c>
+      <c r="F8">
+        <v>17372744</v>
+      </c>
+      <c r="G8">
+        <v>17372744</v>
+      </c>
+      <c r="H8">
+        <v>75627188.46638322</v>
+      </c>
+      <c r="I8">
+        <v>48589152.88376169</v>
       </c>
     </row>
     <row r="9">
@@ -1355,13 +1768,28 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>130776854</v>
+        <v>5086945</v>
       </c>
       <c r="C13">
-        <v>61541250</v>
+        <v>4542522</v>
       </c>
       <c r="D13">
-        <v>39539182</v>
+        <v>201227660.6077402</v>
+      </c>
+      <c r="E13">
+        <v>160709863.7666146</v>
+      </c>
+      <c r="F13">
+        <v>17372744</v>
+      </c>
+      <c r="G13">
+        <v>17372744</v>
+      </c>
+      <c r="H13">
+        <v>75627188.46638322</v>
+      </c>
+      <c r="I13">
+        <v>48589152.88376169</v>
       </c>
     </row>
     <row r="14"/>
@@ -1370,16 +1798,31 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-31602885</v>
+        <v>-49267221</v>
       </c>
       <c r="C15">
-        <v>-25619408</v>
+        <v>-21046127</v>
       </c>
       <c r="D15">
-        <v>-12011187</v>
+        <v>-109962673.81625389</v>
       </c>
       <c r="E15">
-        <v>-2005582</v>
+        <v>-38836347.47003463</v>
+      </c>
+      <c r="F15">
+        <v>-29886064</v>
+      </c>
+      <c r="G15">
+        <v>-16325484</v>
+      </c>
+      <c r="H15">
+        <v>-31483335.722331792</v>
+      </c>
+      <c r="I15">
+        <v>-14760381.270873303</v>
+      </c>
+      <c r="J15">
+        <v>-2464631.9293838837</v>
       </c>
     </row>
     <row r="16">
@@ -1387,13 +1830,28 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-2514614</v>
+        <v>-2994974</v>
       </c>
       <c r="C16">
-        <v>-39346</v>
+        <v>-2994974</v>
       </c>
       <c r="D16">
-        <v>-39347</v>
+        <v>-6809440.642522348</v>
+      </c>
+      <c r="E16">
+        <v>-3090174.300764429</v>
+      </c>
+      <c r="F16">
+        <v>-1636937</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>-48352.21729887561</v>
+      </c>
+      <c r="I16">
+        <v>-48352.983086938184</v>
       </c>
     </row>
     <row r="17">
@@ -1406,16 +1864,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>13145532</v>
+        <v>138374400</v>
       </c>
       <c r="C18">
-        <v>404742</v>
+        <v>-1576796</v>
       </c>
       <c r="D18">
-        <v>181803</v>
+        <v>15825454.622902956</v>
       </c>
       <c r="E18">
-        <v>350089</v>
+        <v>16154362.12328271</v>
+      </c>
+      <c r="F18">
+        <v>12884139</v>
+      </c>
+      <c r="G18">
+        <v>12562552</v>
+      </c>
+      <c r="H18">
+        <v>497381.3362958789</v>
+      </c>
+      <c r="I18">
+        <v>223415.1875404637</v>
+      </c>
+      <c r="J18">
+        <v>430219.5210797038</v>
       </c>
     </row>
     <row r="19">
@@ -1423,16 +1896,31 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-9533996</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>-1160037</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>-2773135</v>
+        <v>-8374486.27625951</v>
       </c>
       <c r="E19">
-        <v>-139609</v>
+        <v>-11716195.576255785</v>
+      </c>
+      <c r="F19">
+        <v>-9930591</v>
+      </c>
+      <c r="G19">
+        <v>-7839988</v>
+      </c>
+      <c r="H19">
+        <v>-1425553.1373869837</v>
+      </c>
+      <c r="I19">
+        <v>-3407867.1754592815</v>
+      </c>
+      <c r="J19">
+        <v>-171563.56560307913</v>
       </c>
     </row>
     <row r="20">
@@ -1445,16 +1933,31 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>100270891</v>
+        <v>91199150</v>
       </c>
       <c r="C21">
-        <v>35127201</v>
+        <v>-21075375</v>
       </c>
       <c r="D21">
-        <v>24897316</v>
+        <v>91906514.49560742</v>
       </c>
       <c r="E21">
-        <v>-1795102</v>
+        <v>123221508.54284248</v>
+      </c>
+      <c r="F21">
+        <v>-11196709</v>
+      </c>
+      <c r="G21">
+        <v>5769824</v>
+      </c>
+      <c r="H21">
+        <v>43167328.72566146</v>
+      </c>
+      <c r="I21">
+        <v>30595966.64188263</v>
+      </c>
+      <c r="J21">
+        <v>-2205975.973907259</v>
       </c>
     </row>
     <row r="22"/>
@@ -1473,13 +1976,49 @@
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
       <c r="B25">
-        <v>4237839</v>
+        <v>84602033</v>
+      </c>
+      <c r="C25">
+        <v>81756621</v>
+      </c>
+      <c r="D25">
+        <v>8523202.90602669</v>
+      </c>
+      <c r="E25">
+        <v>5207821.625337817</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>111370901</v>
+      </c>
+      <c r="D26">
+        <v>-150798383.49294367</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1516,16 +2055,31 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>104508730</v>
+        <v>175801183</v>
       </c>
       <c r="C33">
-        <v>35127201</v>
+        <v>172052147</v>
       </c>
       <c r="D33">
-        <v>24897316</v>
+        <v>-50368666.091309585</v>
       </c>
       <c r="E33">
-        <v>-1795102</v>
+        <v>128429330.1681803</v>
+      </c>
+      <c r="F33">
+        <v>-11196709</v>
+      </c>
+      <c r="G33">
+        <v>5769824</v>
+      </c>
+      <c r="H33">
+        <v>43167328.72566146</v>
+      </c>
+      <c r="I33">
+        <v>30595966.64188263</v>
+      </c>
+      <c r="J33">
+        <v>-2205975.973907259</v>
       </c>
     </row>
     <row r="34"/>
@@ -1534,16 +2088,31 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>1126959</v>
+        <v>2597079</v>
       </c>
       <c r="C35">
-        <v>2973517</v>
+        <v>1924259</v>
       </c>
       <c r="D35">
-        <v>1772256</v>
+        <v>6981529.080782728</v>
       </c>
       <c r="E35">
-        <v>2228726</v>
+        <v>1384904.2993537695</v>
+      </c>
+      <c r="F35">
+        <v>1384904</v>
+      </c>
+      <c r="G35">
+        <v>809516</v>
+      </c>
+      <c r="H35">
+        <v>3654114.604845939</v>
+      </c>
+      <c r="I35">
+        <v>2177900.8410736457</v>
+      </c>
+      <c r="J35">
+        <v>2738850.498981356</v>
       </c>
     </row>
     <row r="36">
@@ -1551,16 +2120,31 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-1817116</v>
+        <v>-3145512</v>
       </c>
       <c r="C36">
-        <v>-3084099</v>
+        <v>-2099824</v>
       </c>
       <c r="D36">
-        <v>-360313</v>
+        <v>-4850144.26514356</v>
       </c>
       <c r="E36">
-        <v>-118444</v>
+        <v>-2233028.6734695095</v>
+      </c>
+      <c r="F36">
+        <v>-84447</v>
+      </c>
+      <c r="G36">
+        <v>-13605</v>
+      </c>
+      <c r="H36">
+        <v>-3790006.003278437</v>
+      </c>
+      <c r="I36">
+        <v>-442783.65301049536</v>
+      </c>
+      <c r="J36">
+        <v>-145554.1903766312</v>
       </c>
     </row>
     <row r="37">
@@ -1568,16 +2152,31 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>48467383</v>
+        <v>-92744094</v>
       </c>
       <c r="C37">
-        <v>-302711543</v>
+        <v>15895367</v>
       </c>
       <c r="D37">
-        <v>-309488201</v>
+        <v>65979458.53722819</v>
       </c>
       <c r="E37">
-        <v>182418757</v>
+        <v>59560895.378736764</v>
+      </c>
+      <c r="F37">
+        <v>-6686050</v>
+      </c>
+      <c r="G37">
+        <v>-25314455</v>
+      </c>
+      <c r="H37">
+        <v>-371998020.48631</v>
+      </c>
+      <c r="I37">
+        <v>-380325761.77497464</v>
+      </c>
+      <c r="J37">
+        <v>224171882.78550556</v>
       </c>
     </row>
     <row r="38">
@@ -1585,16 +2184,31 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>152285956</v>
+        <v>82508656</v>
       </c>
       <c r="C38">
-        <v>-267694924</v>
+        <v>187771949</v>
       </c>
       <c r="D38">
-        <v>-283178942</v>
+        <v>17742177.261557773</v>
       </c>
       <c r="E38">
-        <v>182733937</v>
+        <v>187142101.17280132</v>
+      </c>
+      <c r="F38">
+        <v>-16582302</v>
+      </c>
+      <c r="G38">
+        <v>-18748720</v>
+      </c>
+      <c r="H38">
+        <v>-328966583.15908104</v>
+      </c>
+      <c r="I38">
+        <v>-347994677.94502884</v>
+      </c>
+      <c r="J38">
+        <v>224559203.12020305</v>
       </c>
     </row>
     <row r="39"/>
@@ -1602,8 +2216,26 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
-      <c r="E40">
-        <v>-48287157</v>
+      <c r="B40">
+        <v>67610111</v>
+      </c>
+      <c r="C40">
+        <v>10142166</v>
+      </c>
+      <c r="D40">
+        <v>50193674.871372595</v>
+      </c>
+      <c r="F40">
+        <v>-39768002</v>
+      </c>
+      <c r="G40">
+        <v>-20009836</v>
+      </c>
+      <c r="H40">
+        <v>-40553790.10713829</v>
+      </c>
+      <c r="J40">
+        <v>-59339418.14464455</v>
       </c>
     </row>
     <row r="41">
@@ -1611,7 +2243,25 @@
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
       <c r="B41">
-        <v>-12459558</v>
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>-15311378.179905085</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1619,16 +2269,31 @@
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-61345140</v>
+        <v>67610111</v>
       </c>
       <c r="C42">
-        <v>-33000446</v>
+        <v>10142166</v>
       </c>
       <c r="D42">
-        <v>54577410</v>
+        <v>50193674.871372595</v>
       </c>
       <c r="E42">
-        <v>-48287157</v>
+        <v>-75386192.51495299</v>
+      </c>
+      <c r="F42">
+        <v>-39768002</v>
+      </c>
+      <c r="G42">
+        <v>-20009836</v>
+      </c>
+      <c r="H42">
+        <v>-40553790.10713829</v>
+      </c>
+      <c r="I42">
+        <v>67069422.89523703</v>
+      </c>
+      <c r="J42">
+        <v>-59339418.14464455</v>
       </c>
     </row>
     <row r="43">
@@ -1636,16 +2301,31 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>152285956</v>
+        <v>150118767</v>
       </c>
       <c r="C43">
-        <v>-267694924</v>
+        <v>197914115</v>
       </c>
       <c r="D43">
-        <v>-283178942</v>
+        <v>67935852.13293037</v>
       </c>
       <c r="E43">
-        <v>134446780</v>
+        <v>187142101.17280132</v>
+      </c>
+      <c r="F43">
+        <v>-56350304</v>
+      </c>
+      <c r="G43">
+        <v>-38758556</v>
+      </c>
+      <c r="H43">
+        <v>-369520373.2662193</v>
+      </c>
+      <c r="I43">
+        <v>-347994677.94502884</v>
+      </c>
+      <c r="J43">
+        <v>165219784.9755585</v>
       </c>
     </row>
     <row r="44">
@@ -1659,38 +2339,86 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>78481258</v>
+        <v>150118767</v>
       </c>
       <c r="C46">
-        <v>-300695370</v>
+        <v>197914115</v>
       </c>
       <c r="D46">
-        <v>-228601532</v>
+        <v>67935852.13293037</v>
       </c>
       <c r="E46">
-        <v>134446780</v>
+        <v>96444530.47794324</v>
+      </c>
+      <c r="F46">
+        <v>-56350304</v>
+      </c>
+      <c r="G46">
+        <v>-38758556</v>
+      </c>
+      <c r="H46">
+        <v>-369520373.2662193</v>
+      </c>
+      <c r="I46">
+        <v>-280925255.0497919</v>
+      </c>
+      <c r="J46">
+        <v>165219784.9755585</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>78481258</v>
+        <v>150118767</v>
       </c>
       <c r="C48">
-        <v>-300695370</v>
+        <v>197914115</v>
       </c>
       <c r="D48">
-        <v>-228601532</v>
+        <v>67935852.13293037</v>
       </c>
       <c r="E48">
-        <v>134446780</v>
+        <v>96444530.47794324</v>
+      </c>
+      <c r="F48">
+        <v>-56350304</v>
+      </c>
+      <c r="G48">
+        <v>-38758556</v>
+      </c>
+      <c r="H48">
+        <v>-369520373.2662193</v>
+      </c>
+      <c r="I48">
+        <v>-280925255.0497919</v>
+      </c>
+      <c r="J48">
+        <v>165219784.9755585</v>
       </c>
     </row>
     <row r="49"/>
@@ -1699,25 +2427,48 @@
         <v xml:space="preserve">    Amortisman</v>
       </c>
       <c r="B50">
-        <v>387719</v>
+        <v>801369</v>
+      </c>
+      <c r="C50">
+        <v>400684.92845394317</v>
+      </c>
+      <c r="D50">
+        <v>990747.0598058553</v>
+      </c>
+      <c r="E50">
+        <v>476462.5066583117</v>
+      </c>
+      <c r="F50">
+        <v>323004</v>
+      </c>
+      <c r="G50">
+        <v>161502.48523045256</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:J50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1725,15 +2476,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -1746,8 +2512,26 @@
       <c r="A3" t="str">
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
+      <c r="B3">
+        <v>14933712</v>
+      </c>
       <c r="C3">
-        <v>883377526</v>
+        <v>7953620</v>
+      </c>
+      <c r="D3">
+        <v>77427540.40595776</v>
+      </c>
+      <c r="E3">
+        <v>281216803.42548454</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>33288289</v>
+      </c>
+      <c r="H3">
+        <v>1085570400.8380718</v>
       </c>
     </row>
     <row r="4">
@@ -1769,16 +2553,52 @@
       <c r="A7" t="str">
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
+      <c r="B7">
+        <v>-14389289</v>
+      </c>
       <c r="C7">
-        <v>-861375458</v>
+        <v>-3411098</v>
+      </c>
+      <c r="D7">
+        <v>-36909743.56483218</v>
+      </c>
+      <c r="E7">
+        <v>-137879683.65886992</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>-15915545</v>
+      </c>
+      <c r="H7">
+        <v>-1058532365.255451</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
+      <c r="B8">
+        <v>544423</v>
+      </c>
       <c r="C8">
-        <v>22002068</v>
+        <v>4542522</v>
+      </c>
+      <c r="D8">
+        <v>40517796.84112561</v>
+      </c>
+      <c r="E8">
+        <v>143337119.7666146</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>17372744</v>
+      </c>
+      <c r="H8">
+        <v>27038035.58262153</v>
       </c>
     </row>
     <row r="9">
@@ -1805,8 +2625,26 @@
       <c r="A13" t="str">
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
+      <c r="B13">
+        <v>544423</v>
+      </c>
       <c r="C13">
-        <v>22002068</v>
+        <v>4542522</v>
+      </c>
+      <c r="D13">
+        <v>40517796.84112561</v>
+      </c>
+      <c r="E13">
+        <v>143337119.7666146</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>17372744</v>
+      </c>
+      <c r="H13">
+        <v>27038035.58262153</v>
       </c>
     </row>
     <row r="14"/>
@@ -1814,16 +2652,52 @@
       <c r="A15" t="str">
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
+      <c r="B15">
+        <v>-28221094</v>
+      </c>
       <c r="C15">
-        <v>-13608221</v>
+        <v>-21046127</v>
+      </c>
+      <c r="D15">
+        <v>-71126326.34621926</v>
+      </c>
+      <c r="E15">
+        <v>-8950283.47003463</v>
+      </c>
+      <c r="F15">
+        <v>-13560580</v>
+      </c>
+      <c r="G15">
+        <v>-16325484</v>
+      </c>
+      <c r="H15">
+        <v>-16722954.45145849</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
+      <c r="B16">
+        <v>0</v>
+      </c>
       <c r="C16">
-        <v>1</v>
+        <v>-2994974</v>
+      </c>
+      <c r="D16">
+        <v>-3719266.341757919</v>
+      </c>
+      <c r="E16">
+        <v>-1453237.300764429</v>
+      </c>
+      <c r="F16">
+        <v>-1636937</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0.7657880625774851</v>
       </c>
     </row>
     <row r="17">
@@ -1835,16 +2709,52 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
+      <c r="B18">
+        <v>139951196</v>
+      </c>
       <c r="C18">
-        <v>222939</v>
+        <v>-1576796</v>
+      </c>
+      <c r="D18">
+        <v>-328907.50037975423</v>
+      </c>
+      <c r="E18">
+        <v>3270223.12328271</v>
+      </c>
+      <c r="F18">
+        <v>321587</v>
+      </c>
+      <c r="G18">
+        <v>12562552</v>
+      </c>
+      <c r="H18">
+        <v>273966.1487554152</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
+      <c r="B19">
+        <v>0</v>
+      </c>
       <c r="C19">
-        <v>1613098</v>
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>3341709.2999962755</v>
+      </c>
+      <c r="E19">
+        <v>-1785604.5762557853</v>
+      </c>
+      <c r="F19">
+        <v>-2090603</v>
+      </c>
+      <c r="G19">
+        <v>-7839988</v>
+      </c>
+      <c r="H19">
+        <v>1982314.0380722978</v>
       </c>
     </row>
     <row r="20">
@@ -1856,8 +2766,26 @@
       <c r="A21" t="str">
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
+      <c r="B21">
+        <v>112274525</v>
+      </c>
       <c r="C21">
-        <v>10229885</v>
+        <v>-21075375</v>
+      </c>
+      <c r="D21">
+        <v>-31314994.047235057</v>
+      </c>
+      <c r="E21">
+        <v>134418217.54284248</v>
+      </c>
+      <c r="F21">
+        <v>-16966533</v>
+      </c>
+      <c r="G21">
+        <v>5769824</v>
+      </c>
+      <c r="H21">
+        <v>12571362.083778828</v>
       </c>
     </row>
     <row r="22"/>
@@ -1875,11 +2803,41 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
+      <c r="B25">
+        <v>2845412</v>
+      </c>
+      <c r="C25">
+        <v>81756621</v>
+      </c>
+      <c r="D25">
+        <v>3315381.2806888726</v>
+      </c>
+      <c r="E25">
+        <v>5207821.625337817</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
+      <c r="B26">
+        <v>-111370901</v>
+      </c>
+      <c r="C26">
+        <v>111370901</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -1915,8 +2873,26 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
+      <c r="B33">
+        <v>3749036</v>
+      </c>
       <c r="C33">
-        <v>10229885</v>
+        <v>172052147</v>
+      </c>
+      <c r="D33">
+        <v>-178797996.2594899</v>
+      </c>
+      <c r="E33">
+        <v>139626039.1681803</v>
+      </c>
+      <c r="F33">
+        <v>-16966533</v>
+      </c>
+      <c r="G33">
+        <v>5769824</v>
+      </c>
+      <c r="H33">
+        <v>12571362.083778828</v>
       </c>
     </row>
     <row r="34"/>
@@ -1924,32 +2900,104 @@
       <c r="A35" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
+      <c r="B35">
+        <v>672820</v>
+      </c>
       <c r="C35">
-        <v>1201261</v>
+        <v>1924259</v>
+      </c>
+      <c r="D35">
+        <v>5596624.781428959</v>
+      </c>
+      <c r="E35">
+        <v>0.2993537695147097</v>
+      </c>
+      <c r="F35">
+        <v>575388</v>
+      </c>
+      <c r="G35">
+        <v>809516</v>
+      </c>
+      <c r="H35">
+        <v>1476213.7637722935</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
+      <c r="B36">
+        <v>-1045688</v>
+      </c>
       <c r="C36">
-        <v>-2723786</v>
+        <v>-2099824</v>
+      </c>
+      <c r="D36">
+        <v>-2617115.591674051</v>
+      </c>
+      <c r="E36">
+        <v>-2148581.6734695095</v>
+      </c>
+      <c r="F36">
+        <v>-70842</v>
+      </c>
+      <c r="G36">
+        <v>-13605</v>
+      </c>
+      <c r="H36">
+        <v>-3347222.3502679416</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
+      <c r="B37">
+        <v>-108639461</v>
+      </c>
       <c r="C37">
-        <v>6776658</v>
+        <v>15895367</v>
+      </c>
+      <c r="D37">
+        <v>6418563.158491425</v>
+      </c>
+      <c r="E37">
+        <v>66246945.378736764</v>
+      </c>
+      <c r="F37">
+        <v>18628405</v>
+      </c>
+      <c r="G37">
+        <v>-25314455</v>
+      </c>
+      <c r="H37">
+        <v>8327741.288664639</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
+      <c r="B38">
+        <v>-105263293</v>
+      </c>
       <c r="C38">
-        <v>15484018</v>
+        <v>187771949</v>
+      </c>
+      <c r="D38">
+        <v>-169399923.91124356</v>
+      </c>
+      <c r="E38">
+        <v>203724403.17280132</v>
+      </c>
+      <c r="F38">
+        <v>2166418</v>
+      </c>
+      <c r="G38">
+        <v>-18748720</v>
+      </c>
+      <c r="H38">
+        <v>19028094.7859478</v>
       </c>
     </row>
     <row r="39"/>
@@ -1957,26 +3005,92 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B40">
+        <v>57467945</v>
+      </c>
+      <c r="C40">
+        <v>10142166</v>
+      </c>
+      <c r="F40">
+        <v>-19758166</v>
+      </c>
+      <c r="G40">
+        <v>-20009836</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>15311378.179905085</v>
+      </c>
+      <c r="E41">
+        <v>-15311378.179905085</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B42">
+        <v>57467945</v>
+      </c>
       <c r="C42">
-        <v>-87577856</v>
+        <v>10142166</v>
+      </c>
+      <c r="D42">
+        <v>125579867.38632558</v>
+      </c>
+      <c r="E42">
+        <v>-35618190.51495299</v>
+      </c>
+      <c r="F42">
+        <v>-19758166</v>
+      </c>
+      <c r="G42">
+        <v>-20009836</v>
+      </c>
+      <c r="H42">
+        <v>-107623213.00237532</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
+      <c r="B43">
+        <v>-47795348</v>
+      </c>
       <c r="C43">
-        <v>15484018</v>
+        <v>197914115</v>
+      </c>
+      <c r="D43">
+        <v>-119206249.03987095</v>
+      </c>
+      <c r="E43">
+        <v>243492405.17280132</v>
+      </c>
+      <c r="F43">
+        <v>-17591748</v>
+      </c>
+      <c r="G43">
+        <v>-38758556</v>
+      </c>
+      <c r="H43">
+        <v>-21525695.321190476</v>
       </c>
     </row>
     <row r="44">
@@ -1989,21 +3103,69 @@
       <c r="A46" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
+      <c r="B46">
+        <v>-47795348</v>
+      </c>
       <c r="C46">
-        <v>-72093838</v>
+        <v>197914115</v>
+      </c>
+      <c r="D46">
+        <v>-28508678.345012873</v>
+      </c>
+      <c r="E46">
+        <v>152794834.47794324</v>
+      </c>
+      <c r="F46">
+        <v>-17591748</v>
+      </c>
+      <c r="G46">
+        <v>-38758556</v>
+      </c>
+      <c r="H46">
+        <v>-88595118.21642745</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
+      <c r="B48">
+        <v>-47795348</v>
+      </c>
       <c r="C48">
-        <v>-72093838</v>
+        <v>197914115</v>
+      </c>
+      <c r="D48">
+        <v>-28508678.345012873</v>
+      </c>
+      <c r="E48">
+        <v>152794834.47794324</v>
+      </c>
+      <c r="F48">
+        <v>-17591748</v>
+      </c>
+      <c r="G48">
+        <v>-38758556</v>
+      </c>
+      <c r="H48">
+        <v>-88595118.21642745</v>
       </c>
     </row>
     <row r="49"/>
@@ -2011,23 +3173,46 @@
       <c r="A50" t="str">
         <v xml:space="preserve">    Amortisman</v>
       </c>
+      <c r="B50">
+        <v>400684.07154605683</v>
+      </c>
+      <c r="C50">
+        <v>400684.92845394317</v>
+      </c>
+      <c r="D50">
+        <v>514284.5531475436</v>
+      </c>
+      <c r="E50">
+        <v>153458.5066583117</v>
+      </c>
+      <c r="F50">
+        <v>161501.51476954744</v>
+      </c>
+      <c r="G50">
+        <v>161502.48523045256</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:J50"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2035,15 +3220,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2057,10 +3257,19 @@
         <v xml:space="preserve">    Satış Gelirleri</v>
       </c>
       <c r="B3">
-        <v>1139304484</v>
+        <v>381531675.8314423</v>
       </c>
       <c r="C3">
-        <v>2433120321</v>
+        <v>366597963.8314423</v>
+      </c>
+      <c r="D3">
+        <v>391932632.8314423</v>
+      </c>
+      <c r="E3">
+        <v>1400075493.2635565</v>
+      </c>
+      <c r="H3">
+        <v>2990027847.549113</v>
       </c>
     </row>
     <row r="4">
@@ -2083,10 +3292,19 @@
         <v xml:space="preserve">    Satışların Maliyeti (-)</v>
       </c>
       <c r="B7">
-        <v>-986525562</v>
+        <v>-192589814.2237021</v>
       </c>
       <c r="C7">
-        <v>-2371579071</v>
+        <v>-178200525.2237021</v>
+      </c>
+      <c r="D7">
+        <v>-190704972.2237021</v>
+      </c>
+      <c r="E7">
+        <v>-1212327593.914321</v>
+      </c>
+      <c r="H7">
+        <v>-2914400659.08273</v>
       </c>
     </row>
     <row r="8">
@@ -2094,10 +3312,19 @@
         <v xml:space="preserve">    Ticari Faaliyetlerden Brüt Kar (Zarar)</v>
       </c>
       <c r="B8">
-        <v>152778922</v>
+        <v>188941861.6077402</v>
       </c>
       <c r="C8">
-        <v>61541250</v>
+        <v>188397438.6077402</v>
+      </c>
+      <c r="D8">
+        <v>201227660.6077402</v>
+      </c>
+      <c r="E8">
+        <v>187747899.34923613</v>
+      </c>
+      <c r="H8">
+        <v>75627188.46638322</v>
       </c>
     </row>
     <row r="9">
@@ -2125,10 +3352,19 @@
         <v xml:space="preserve">    Brüt Kar (Zarar)</v>
       </c>
       <c r="B13">
-        <v>152778922</v>
+        <v>188941861.6077402</v>
       </c>
       <c r="C13">
-        <v>61541250</v>
+        <v>188397438.6077402</v>
+      </c>
+      <c r="D13">
+        <v>201227660.6077402</v>
+      </c>
+      <c r="E13">
+        <v>187747899.34923613</v>
+      </c>
+      <c r="H13">
+        <v>75627188.46638322</v>
       </c>
     </row>
     <row r="14"/>
@@ -2137,13 +3373,22 @@
         <v xml:space="preserve">    Genel Yönetim Giderleri (-)</v>
       </c>
       <c r="B15">
-        <v>-45211106</v>
+        <v>-129343830.81625389</v>
       </c>
       <c r="C15">
-        <v>-25619408</v>
+        <v>-114683316.81625389</v>
+      </c>
+      <c r="D15">
+        <v>-109962673.81625389</v>
       </c>
       <c r="E15">
-        <v>-2005582</v>
+        <v>-55559301.92149312</v>
+      </c>
+      <c r="H15">
+        <v>-31483335.722331792</v>
+      </c>
+      <c r="J15">
+        <v>-2464631.9293838837</v>
       </c>
     </row>
     <row r="16">
@@ -2151,10 +3396,19 @@
         <v xml:space="preserve">    Pazarlama, Satış ve Dağıtım Giderleri (-)</v>
       </c>
       <c r="B16">
-        <v>-2514613</v>
+        <v>-8167477.642522348</v>
       </c>
       <c r="C16">
-        <v>-39346</v>
+        <v>-9804414.642522348</v>
+      </c>
+      <c r="D16">
+        <v>-6809440.642522348</v>
+      </c>
+      <c r="E16">
+        <v>-3090173.5349763664</v>
+      </c>
+      <c r="H16">
+        <v>-48352.21729887561</v>
       </c>
     </row>
     <row r="17">
@@ -2167,13 +3421,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Gelirleri</v>
       </c>
       <c r="B18">
-        <v>13368471</v>
+        <v>141315715.62290296</v>
       </c>
       <c r="C18">
-        <v>404742</v>
+        <v>1686106.6229029559</v>
+      </c>
+      <c r="D18">
+        <v>15825454.622902956</v>
       </c>
       <c r="E18">
-        <v>350089</v>
+        <v>16428328.272038125</v>
+      </c>
+      <c r="H18">
+        <v>497381.3362958789</v>
+      </c>
+      <c r="J18">
+        <v>430219.5210797038</v>
       </c>
     </row>
     <row r="19">
@@ -2181,13 +3444,22 @@
         <v xml:space="preserve">    Diğer Faaliyet Giderleri (-)</v>
       </c>
       <c r="B19">
-        <v>-7920898</v>
+        <v>1556104.7237404902</v>
       </c>
       <c r="C19">
-        <v>-1160037</v>
+        <v>-534498.2762595098</v>
+      </c>
+      <c r="D19">
+        <v>-8374486.27625951</v>
       </c>
       <c r="E19">
-        <v>-139609</v>
+        <v>-9733881.538183488</v>
+      </c>
+      <c r="H19">
+        <v>-1425553.1373869837</v>
+      </c>
+      <c r="J19">
+        <v>-171563.56560307913</v>
       </c>
     </row>
     <row r="20">
@@ -2200,13 +3472,22 @@
         <v xml:space="preserve">    Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B21">
-        <v>110500776</v>
+        <v>194302373.49560744</v>
       </c>
       <c r="C21">
-        <v>35127201</v>
+        <v>65061315.49560742</v>
+      </c>
+      <c r="D21">
+        <v>91906514.49560742</v>
       </c>
       <c r="E21">
-        <v>-1795102</v>
+        <v>135792870.6266213</v>
+      </c>
+      <c r="H21">
+        <v>43167328.72566146</v>
+      </c>
+      <c r="J21">
+        <v>-2205975.973907259</v>
       </c>
     </row>
     <row r="22"/>
@@ -2224,11 +3505,35 @@
       <c r="A25" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Gelirler</v>
       </c>
+      <c r="B25">
+        <v>93125235.90602669</v>
+      </c>
+      <c r="C25">
+        <v>90279823.90602669</v>
+      </c>
+      <c r="D25">
+        <v>8523202.90602669</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Giderler (-)</v>
       </c>
+      <c r="B26">
+        <v>-150798383.49294367</v>
+      </c>
+      <c r="C26">
+        <v>-39427482.492943674</v>
+      </c>
+      <c r="D26">
+        <v>-150798383.49294367</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -2265,13 +3570,22 @@
         <v xml:space="preserve">    Finansman Geliri (Gideri) Öncesi Faaliyet Karı (Zararı)</v>
       </c>
       <c r="B33">
-        <v>114738615</v>
+        <v>136629225.90869042</v>
       </c>
       <c r="C33">
-        <v>35127201</v>
+        <v>115913656.90869042</v>
+      </c>
+      <c r="D33">
+        <v>-50368666.091309585</v>
       </c>
       <c r="E33">
-        <v>-1795102</v>
+        <v>141000692.25195915</v>
+      </c>
+      <c r="H33">
+        <v>43167328.72566146</v>
+      </c>
+      <c r="J33">
+        <v>-2205975.973907259</v>
       </c>
     </row>
     <row r="34"/>
@@ -2280,13 +3594,22 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Gelirler</v>
       </c>
       <c r="B35">
-        <v>2328220</v>
+        <v>8193704.080782728</v>
       </c>
       <c r="C35">
-        <v>2973517</v>
+        <v>8096272.080782728</v>
+      </c>
+      <c r="D35">
+        <v>6981529.080782728</v>
       </c>
       <c r="E35">
-        <v>2228726</v>
+        <v>2861118.063126063</v>
+      </c>
+      <c r="H35">
+        <v>3654114.604845939</v>
+      </c>
+      <c r="J35">
+        <v>2738850.498981356</v>
       </c>
     </row>
     <row r="36">
@@ -2294,13 +3617,22 @@
         <v xml:space="preserve">    (Esas Faaliyet Dışı) Finansal Giderler (-)</v>
       </c>
       <c r="B36">
-        <v>-4540902</v>
+        <v>-7911209.26514356</v>
       </c>
       <c r="C36">
-        <v>-3084099</v>
+        <v>-6936363.26514356</v>
+      </c>
+      <c r="D36">
+        <v>-4850144.26514356</v>
       </c>
       <c r="E36">
-        <v>-118444</v>
+        <v>-5580251.023737451</v>
+      </c>
+      <c r="H36">
+        <v>-3790006.003278437</v>
+      </c>
+      <c r="J36">
+        <v>-145554.1903766312</v>
       </c>
     </row>
     <row r="37">
@@ -2308,13 +3640,22 @@
         <v xml:space="preserve">    Net Parasal Pozisyon Kazançları (Kayıpları)</v>
       </c>
       <c r="B37">
-        <v>55244041</v>
+        <v>-20078585.462771803</v>
       </c>
       <c r="C37">
-        <v>-302711543</v>
+        <v>107189280.5372282</v>
+      </c>
+      <c r="D37">
+        <v>65979458.53722819</v>
       </c>
       <c r="E37">
-        <v>182418757</v>
+        <v>67888636.6674014</v>
+      </c>
+      <c r="H37">
+        <v>-371998020.48631</v>
+      </c>
+      <c r="J37">
+        <v>224171882.78550556</v>
       </c>
     </row>
     <row r="38">
@@ -2322,13 +3663,22 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Öncesi Karı (Zararı)</v>
       </c>
       <c r="B38">
-        <v>167769974</v>
+        <v>116833135.26155777</v>
       </c>
       <c r="C38">
-        <v>-267694924</v>
+        <v>224262846.26155776</v>
+      </c>
+      <c r="D38">
+        <v>17742177.261557773</v>
       </c>
       <c r="E38">
-        <v>182733937</v>
+        <v>206170195.95874912</v>
+      </c>
+      <c r="H38">
+        <v>-328966583.15908104</v>
+      </c>
+      <c r="J38">
+        <v>224559203.12020305</v>
       </c>
     </row>
     <row r="39"/>
@@ -2336,27 +3686,60 @@
       <c r="A40" t="str">
         <v xml:space="preserve">    Sürdürülen Faaliyetler Vergi Geliri (Gideri)</v>
       </c>
-      <c r="E40">
-        <v>-48287157</v>
+      <c r="B40">
+        <v>157571787.87137258</v>
+      </c>
+      <c r="C40">
+        <v>80345676.8713726</v>
+      </c>
+      <c r="D40">
+        <v>50193674.871372595</v>
+      </c>
+      <c r="H40">
+        <v>-40553790.10713829</v>
+      </c>
+      <c r="J40">
+        <v>-59339418.14464455</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
         <v xml:space="preserve">    Dönem Vergi Geliri (Gideri)</v>
       </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
         <v xml:space="preserve">    Ertelenmiş Vergi Geliri (Gideri)</v>
       </c>
       <c r="B42">
-        <v>-148922996</v>
+        <v>157571787.87137258</v>
       </c>
       <c r="C42">
-        <v>-33000446</v>
+        <v>80345676.8713726</v>
+      </c>
+      <c r="D42">
+        <v>50193674.871372595</v>
       </c>
       <c r="E42">
-        <v>-48287157</v>
+        <v>-183009405.51732832</v>
+      </c>
+      <c r="H42">
+        <v>-40553790.10713829</v>
+      </c>
+      <c r="J42">
+        <v>-59339418.14464455</v>
       </c>
     </row>
     <row r="43">
@@ -2364,13 +3747,22 @@
         <v xml:space="preserve">    Sürdürülen Faaliyetler Dönem Karı/Zararı</v>
       </c>
       <c r="B43">
-        <v>167769974</v>
+        <v>274404923.1329304</v>
       </c>
       <c r="C43">
-        <v>-267694924</v>
+        <v>304608523.1329304</v>
+      </c>
+      <c r="D43">
+        <v>67935852.13293037</v>
       </c>
       <c r="E43">
-        <v>134446780</v>
+        <v>165616405.85161084</v>
+      </c>
+      <c r="H43">
+        <v>-369520373.2662193</v>
+      </c>
+      <c r="J43">
+        <v>165219784.9755585</v>
       </c>
     </row>
     <row r="44">
@@ -2384,32 +3776,62 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B46">
-        <v>6387420</v>
+        <v>274404923.1329304</v>
       </c>
       <c r="C46">
-        <v>-300695370</v>
+        <v>304608523.1329304</v>
+      </c>
+      <c r="D46">
+        <v>67935852.13293037</v>
       </c>
       <c r="E46">
-        <v>134446780</v>
+        <v>7849412.261515796</v>
+      </c>
+      <c r="H46">
+        <v>-369520373.2662193</v>
+      </c>
+      <c r="J46">
+        <v>165219784.9755585</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
         <v xml:space="preserve">    Azınlık Payları</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    Ana Ortaklık Payları</v>
       </c>
       <c r="B48">
-        <v>6387420</v>
+        <v>274404923.1329304</v>
       </c>
       <c r="C48">
-        <v>-300695370</v>
+        <v>304608523.1329304</v>
+      </c>
+      <c r="D48">
+        <v>67935852.13293037</v>
       </c>
       <c r="E48">
-        <v>134446780</v>
+        <v>7849412.261515796</v>
+      </c>
+      <c r="H48">
+        <v>-369520373.2662193</v>
+      </c>
+      <c r="J48">
+        <v>165219784.9755585</v>
       </c>
     </row>
     <row r="49"/>
@@ -2417,23 +3839,40 @@
       <c r="A50" t="str">
         <v xml:space="preserve">    Amortisman</v>
       </c>
+      <c r="B50">
+        <v>1469112.0598058552</v>
+      </c>
+      <c r="C50">
+        <v>1229929.503029346</v>
+      </c>
+      <c r="D50">
+        <v>990747.0598058553</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J50"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:J129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2441,15 +3880,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -2463,16 +3917,31 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-267756559</v>
+        <v>-1033450919</v>
       </c>
       <c r="C3">
-        <v>-763337695</v>
+        <v>-786835915.2576952</v>
       </c>
       <c r="D3">
-        <v>-896389951</v>
+        <v>-822777519.189509</v>
       </c>
       <c r="E3">
-        <v>36857861</v>
+        <v>-329042325.1771105</v>
+      </c>
+      <c r="F3">
+        <v>-508591012</v>
+      </c>
+      <c r="G3">
+        <v>-311227942.3036719</v>
+      </c>
+      <c r="H3">
+        <v>-938055115.599698</v>
+      </c>
+      <c r="I3">
+        <v>-1101561189.925645</v>
+      </c>
+      <c r="J3">
+        <v>45294114.66067855</v>
       </c>
     </row>
     <row r="4">
@@ -2480,16 +3949,31 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>78481258</v>
+        <v>150118767</v>
       </c>
       <c r="C4">
-        <v>-300695370</v>
+        <v>197914115.05068097</v>
       </c>
       <c r="D4">
-        <v>-228601532</v>
+        <v>67935852.13293037</v>
       </c>
       <c r="E4">
-        <v>134446780</v>
+        <v>96444530.47794324</v>
+      </c>
+      <c r="F4">
+        <v>-56350304</v>
+      </c>
+      <c r="G4">
+        <v>-35817009.854960516</v>
+      </c>
+      <c r="H4">
+        <v>-369520373.2662193</v>
+      </c>
+      <c r="I4">
+        <v>-280925255.0497919</v>
+      </c>
+      <c r="J4">
+        <v>165219784.9755585</v>
       </c>
     </row>
     <row r="5">
@@ -2497,16 +3981,31 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>65759925</v>
+        <v>-154003169</v>
       </c>
       <c r="C5">
-        <v>32320623</v>
+        <v>-202943373.58326656</v>
       </c>
       <c r="D5">
-        <v>-55902600</v>
+        <v>79193397.65678868</v>
       </c>
       <c r="E5">
-        <v>46058431</v>
+        <v>80811460.62783247</v>
+      </c>
+      <c r="F5">
+        <v>36632398</v>
+      </c>
+      <c r="G5">
+        <v>14249724.75722702</v>
+      </c>
+      <c r="H5">
+        <v>39718366.007811904</v>
+      </c>
+      <c r="I5">
+        <v>-68697930.52369611</v>
+      </c>
+      <c r="J5">
+        <v>56600567.645663194</v>
       </c>
     </row>
     <row r="6">
@@ -2514,7 +4013,25 @@
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B6">
-        <v>387719</v>
+        <v>801369</v>
+      </c>
+      <c r="C6">
+        <v>400684.92845394317</v>
+      </c>
+      <c r="D6">
+        <v>990747.0598058553</v>
+      </c>
+      <c r="E6">
+        <v>476462.5066583117</v>
+      </c>
+      <c r="F6">
+        <v>323004</v>
+      </c>
+      <c r="G6">
+        <v>161502.48523045256</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -2527,13 +4044,28 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-4787576</v>
+        <v>-5679</v>
       </c>
       <c r="C8">
-        <v>1654686</v>
+        <v>1841949.9805236454</v>
       </c>
       <c r="D8">
-        <v>276149</v>
+        <v>-7358848.305176346</v>
+      </c>
+      <c r="E8">
+        <v>-5883385.807188126</v>
+      </c>
+      <c r="F8">
+        <v>-2073704</v>
+      </c>
+      <c r="G8">
+        <v>-5112097.606663495</v>
+      </c>
+      <c r="H8">
+        <v>2033421.5276490026</v>
+      </c>
+      <c r="I8">
+        <v>339355.6796318625</v>
       </c>
     </row>
     <row r="9">
@@ -2556,16 +4088,31 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>592923</v>
+        <v>-2586715</v>
       </c>
       <c r="C12">
-        <v>-2334509</v>
+        <v>-1916320.0140092173</v>
       </c>
       <c r="D12">
-        <v>-1601339</v>
+        <v>-6981529.080782728</v>
       </c>
       <c r="E12">
-        <v>-2228726</v>
+        <v>728634.8588420121</v>
+      </c>
+      <c r="F12">
+        <v>-1384904</v>
+      </c>
+      <c r="G12">
+        <v>-809515.7170277806</v>
+      </c>
+      <c r="H12">
+        <v>-2868845.6269753864</v>
+      </c>
+      <c r="I12">
+        <v>-1967863.3080909476</v>
+      </c>
+      <c r="J12">
+        <v>-2738850.498981356</v>
       </c>
     </row>
     <row r="13">
@@ -2597,6 +4144,18 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B18">
+        <v>-84602033</v>
+      </c>
+      <c r="D18">
+        <v>143405609.7365213</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -2608,41 +4167,59 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>73804698</v>
+        <v>-67610111</v>
       </c>
       <c r="C20">
-        <v>33000446</v>
+        <v>-10142166.230698213</v>
       </c>
       <c r="D20">
-        <v>-54577410</v>
+        <v>-50193674.871372595</v>
       </c>
       <c r="E20">
-        <v>48287157</v>
+        <v>90697570.69485809</v>
+      </c>
+      <c r="F20">
+        <v>39768002</v>
+      </c>
+      <c r="G20">
+        <v>20009835.595687844</v>
+      </c>
+      <c r="H20">
+        <v>40553790.10713829</v>
+      </c>
+      <c r="I20">
+        <v>-67069422.89523703</v>
+      </c>
+      <c r="J20">
+        <v>59339418.14464455</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="B21">
-        <v>-130665696</v>
-      </c>
-      <c r="C21">
-        <v>-39629662</v>
-      </c>
-      <c r="D21">
-        <v>-26922985</v>
-      </c>
       <c r="E21">
-        <v>17981922</v>
+        <v>-160573263.2406793</v>
+      </c>
+      <c r="I21">
+        <v>-33085283.2072303</v>
+      </c>
+      <c r="J21">
+        <v>22097734.778677963</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B22">
-        <v>-4237839</v>
+      <c r="D22">
+        <v>-668906.8822067977</v>
+      </c>
+      <c r="E22">
+        <v>-5207821.625337817</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2664,6 +4241,12 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım ya da Finansman Faaliyetlerinden Kaynaklanan Nakit Akışlarına Neden Olan Diğer Kalemlere İlişkin Düzeltmeler</v>
       </c>
+      <c r="C26">
+        <v>-193127522.24753672</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -2674,6 +4257,24 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
+      <c r="B28">
+        <v>-1083868607</v>
+      </c>
+      <c r="C28">
+        <v>-865778960.9893554</v>
+      </c>
+      <c r="D28">
+        <v>-861529368.4157213</v>
+      </c>
+      <c r="F28">
+        <v>-402974648</v>
+      </c>
+      <c r="G28">
+        <v>-255082388.47063163</v>
+      </c>
+      <c r="H28">
+        <v>-559718246.6062034</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -2690,13 +4291,28 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-147676353</v>
+        <v>342964736</v>
       </c>
       <c r="C31">
-        <v>-529290590</v>
+        <v>87440469.48846574</v>
       </c>
       <c r="D31">
-        <v>-48825213</v>
+        <v>770024.9580718696</v>
+      </c>
+      <c r="E31">
+        <v>-181477423.9192242</v>
+      </c>
+      <c r="F31">
+        <v>102676719</v>
+      </c>
+      <c r="G31">
+        <v>-11592647.276902508</v>
+      </c>
+      <c r="H31">
+        <v>-650437871.9653971</v>
+      </c>
+      <c r="I31">
+        <v>-60000627.70745304</v>
       </c>
     </row>
     <row r="32">
@@ -2709,30 +4325,42 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>178644697</v>
+        <v>2294744</v>
       </c>
       <c r="C33">
-        <v>-199286781</v>
+        <v>2200922.155218608</v>
       </c>
       <c r="D33">
-        <v>-95837665</v>
+        <v>220592664.75598702</v>
+      </c>
+      <c r="E33">
+        <v>219533992.74689808</v>
+      </c>
+      <c r="F33">
+        <v>218313967</v>
+      </c>
+      <c r="G33">
+        <v>23164200.072107255</v>
+      </c>
+      <c r="H33">
+        <v>-244900763.41818</v>
+      </c>
+      <c r="I33">
+        <v>-117773578.54059137</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B34">
-        <v>778562327</v>
-      </c>
-      <c r="C34">
-        <v>319907867</v>
-      </c>
-      <c r="D34">
-        <v>716965043</v>
-      </c>
       <c r="E34">
-        <v>4006694013</v>
+        <v>956764455.4745786</v>
+      </c>
+      <c r="I34">
+        <v>881068406.6918675</v>
+      </c>
+      <c r="J34">
+        <v>4923770753.681996</v>
       </c>
     </row>
     <row r="35">
@@ -2750,16 +4378,31 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-167762033</v>
+        <v>-937732533</v>
       </c>
       <c r="C37">
-        <v>188079477</v>
+        <v>-829697868.8129175</v>
       </c>
       <c r="D37">
-        <v>141416466</v>
+        <v>-2695118282.8907876</v>
       </c>
       <c r="E37">
-        <v>-2892170272</v>
+        <v>-206160437.7533069</v>
+      </c>
+      <c r="F37">
+        <v>-89320598</v>
+      </c>
+      <c r="G37">
+        <v>-93796142.01012741</v>
+      </c>
+      <c r="H37">
+        <v>231128263.15849194</v>
+      </c>
+      <c r="I37">
+        <v>173784735.52526417</v>
+      </c>
+      <c r="J37">
+        <v>-3554147971.803732</v>
       </c>
     </row>
     <row r="38">
@@ -2772,16 +4415,31 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>-836853790</v>
+        <v>-574276396</v>
       </c>
       <c r="C39">
-        <v>-564137167</v>
+        <v>-156552719.4628809</v>
       </c>
       <c r="D39">
-        <v>-1502425615</v>
+        <v>431814033.8959609</v>
       </c>
       <c r="E39">
-        <v>-674622924</v>
+        <v>-1028398026.6376122</v>
+      </c>
+      <c r="F39">
+        <v>-1220160552</v>
+      </c>
+      <c r="G39">
+        <v>-560717881.0423278</v>
+      </c>
+      <c r="H39">
+        <v>-693260347.872679</v>
+      </c>
+      <c r="I39">
+        <v>-1846310019.8611765</v>
+      </c>
+      <c r="J39">
+        <v>-829034763.3677992</v>
       </c>
     </row>
     <row r="40">
@@ -2789,16 +4447,31 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>12709844</v>
+        <v>-139892218</v>
       </c>
       <c r="C40">
-        <v>2230530</v>
+        <v>-97534002.40873192</v>
       </c>
       <c r="D40">
-        <v>359658</v>
+        <v>604342040.44451</v>
       </c>
       <c r="E40">
-        <v>636105</v>
+        <v>15618951.1772085</v>
+      </c>
+      <c r="F40">
+        <v>13664275</v>
+      </c>
+      <c r="G40">
+        <v>16981795.08903366</v>
+      </c>
+      <c r="H40">
+        <v>2741067.8860487156</v>
+      </c>
+      <c r="I40">
+        <v>441978.73258652544</v>
+      </c>
+      <c r="J40">
+        <v>781700.6202891407</v>
       </c>
     </row>
     <row r="41">
@@ -2811,35 +4484,83 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>-555072</v>
+        <v>-2041141</v>
       </c>
       <c r="C42">
-        <v>1749285</v>
+        <v>-113181.65393070133</v>
       </c>
       <c r="D42">
-        <v>227759</v>
+        <v>138423.2364060139</v>
       </c>
       <c r="E42">
-        <v>559094</v>
+        <v>-682120.2894256985</v>
+      </c>
+      <c r="F42">
+        <v>1001330</v>
+      </c>
+      <c r="G42">
+        <v>1032929.7355446708</v>
+      </c>
+      <c r="H42">
+        <v>2149671.7514023003</v>
+      </c>
+      <c r="I42">
+        <v>279889.87914956553</v>
+      </c>
+      <c r="J42">
+        <v>687062.8694947168</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B43">
+        <v>163836310</v>
+      </c>
+      <c r="C43">
+        <v>79885917.26906388</v>
+      </c>
+      <c r="D43">
+        <v>811254345.0014601</v>
+      </c>
+      <c r="F43">
+        <v>702147471</v>
+      </c>
+      <c r="G43">
+        <v>336768568.6496765</v>
+      </c>
+      <c r="H43">
+        <v>393130345.280793</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
       <c r="C44">
-        <v>-424494</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>-424494</v>
-      </c>
-      <c r="E44">
-        <v>424495</v>
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>385127.3201482386</v>
+      </c>
+      <c r="H44">
+        <v>-521655.1856670851</v>
+      </c>
+      <c r="I44">
+        <v>-521654.7945842565</v>
+      </c>
+      <c r="J44">
+        <v>521656.02347039996</v>
       </c>
     </row>
     <row r="45">
@@ -2856,28 +4577,67 @@
       <c r="A47" t="str">
         <v xml:space="preserve">    Ertelenmiş Gelirlerdeki Artış (Azalış)</v>
       </c>
+      <c r="B47">
+        <v>126138659</v>
+      </c>
+      <c r="F47">
+        <v>75445437</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>-98206872</v>
+        <v>-65160768</v>
       </c>
       <c r="C48">
-        <v>325703928</v>
+        <v>48591502.436357245</v>
       </c>
       <c r="D48">
-        <v>203547851</v>
+        <v>-235322617.81732965</v>
       </c>
       <c r="E48">
-        <v>-602949919</v>
+        <v>-120685064.19389291</v>
+      </c>
+      <c r="F48">
+        <v>-206742697</v>
+      </c>
+      <c r="G48">
+        <v>32691660.99221567</v>
+      </c>
+      <c r="H48">
+        <v>400253043.75898373</v>
+      </c>
+      <c r="I48">
+        <v>250137133.6260862</v>
+      </c>
+      <c r="J48">
+        <v>-740956800.6627635</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>-1087753009</v>
+      </c>
+      <c r="C49">
+        <v>-870808219.5219411</v>
+      </c>
+      <c r="D49">
+        <v>-714400118.6260022</v>
+      </c>
+      <c r="F49">
+        <v>-422692554</v>
+      </c>
+      <c r="G49">
+        <v>-276649673.5683651</v>
+      </c>
+      <c r="H49">
+        <v>-889520253.864611</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -2904,16 +4664,31 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-194794</v>
+        <v>-316863</v>
       </c>
       <c r="C54">
-        <v>134659</v>
+        <v>-329716.8510011017</v>
       </c>
       <c r="D54">
-        <v>33374</v>
+        <v>-239379.98120021517</v>
       </c>
       <c r="E54">
-        <v>-199864</v>
+        <v>-239379.64743022437</v>
+      </c>
+      <c r="F54">
+        <v>-234384</v>
+      </c>
+      <c r="G54">
+        <v>-83795.77388704698</v>
+      </c>
+      <c r="H54">
+        <v>165480.92994903057</v>
+      </c>
+      <c r="I54">
+        <v>41012.84615201858</v>
+      </c>
+      <c r="J54">
+        <v>-245610.1001775946</v>
       </c>
     </row>
     <row r="55">
@@ -2976,6 +4751,24 @@
       <c r="A67" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
+      <c r="B67">
+        <v>1150821438</v>
+      </c>
+      <c r="C67">
+        <v>872207761.1189116</v>
+      </c>
+      <c r="D67">
+        <v>-1207951759.1199706</v>
+      </c>
+      <c r="F67">
+        <v>-1842451</v>
+      </c>
+      <c r="G67">
+        <v>-2418807.86141556</v>
+      </c>
+      <c r="H67">
+        <v>2889185.117895654</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3016,18 +4809,57 @@
       <c r="A75" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
+      <c r="B75">
+        <v>1148234723</v>
+      </c>
+      <c r="C75">
+        <v>2708042995.882563</v>
+      </c>
+      <c r="D75">
+        <v>1044531089.3587073</v>
+      </c>
+      <c r="F75">
+        <v>2686</v>
+      </c>
+      <c r="G75">
+        <v>1716.494959578353</v>
+      </c>
+      <c r="H75">
+        <v>20339.490920267403</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
+      <c r="C76">
+        <v>-1837751554.7776606</v>
+      </c>
+      <c r="D76">
+        <v>-2251569389.60021</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B77">
-        <v>12965586</v>
+        <v>1797171</v>
+      </c>
+      <c r="C77">
+        <v>1797171.2928125504</v>
+      </c>
+      <c r="D77">
+        <v>17983042.19516943</v>
+      </c>
+      <c r="E77">
+        <v>15933228.977310661</v>
+      </c>
+      <c r="F77">
+        <v>7818370</v>
       </c>
     </row>
     <row r="78">
@@ -3035,7 +4867,22 @@
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
       <c r="B78">
-        <v>-16483123</v>
+        <v>-1797171</v>
+      </c>
+      <c r="C78">
+        <v>-1797171.2928125504</v>
+      </c>
+      <c r="D78">
+        <v>-25878030.15441949</v>
+      </c>
+      <c r="E78">
+        <v>-20255881.45573797</v>
+      </c>
+      <c r="F78">
+        <v>-11048411</v>
+      </c>
+      <c r="G78">
+        <v>-3230040.073402919</v>
       </c>
     </row>
     <row r="79">
@@ -3117,6 +4964,24 @@
       <c r="A94" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
+      <c r="B94">
+        <v>2586715</v>
+      </c>
+      <c r="C94">
+        <v>1916320.0140092173</v>
+      </c>
+      <c r="D94">
+        <v>6981529.080782728</v>
+      </c>
+      <c r="F94">
+        <v>1384904</v>
+      </c>
+      <c r="G94">
+        <v>809515.7170277806</v>
+      </c>
+      <c r="H94">
+        <v>2868845.6269753864</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -3137,17 +5002,14 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B98">
-        <v>1126959</v>
-      </c>
-      <c r="C98">
-        <v>2334509</v>
-      </c>
-      <c r="D98">
-        <v>1601339</v>
-      </c>
       <c r="E98">
-        <v>2228726</v>
+        <v>1384904.2993537695</v>
+      </c>
+      <c r="I98">
+        <v>1967863.3080909476</v>
+      </c>
+      <c r="J98">
+        <v>2738850.498981356</v>
       </c>
     </row>
     <row r="99">
@@ -3161,16 +5023,31 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>368597643</v>
+        <v>-126664280</v>
       </c>
       <c r="C101">
-        <v>708100108</v>
+        <v>-91863151.4484372</v>
       </c>
       <c r="D101">
-        <v>836592776</v>
+        <v>2040560833.8067007</v>
       </c>
       <c r="E101">
-        <v>42299741</v>
+        <v>452964535.996754</v>
+      </c>
+      <c r="F101">
+        <v>509309300</v>
+      </c>
+      <c r="G101">
+        <v>324819105.5181187</v>
+      </c>
+      <c r="H101">
+        <v>870174410.430628</v>
+      </c>
+      <c r="I101">
+        <v>1028077270.1497617</v>
+      </c>
+      <c r="J101">
+        <v>51981565.58708075</v>
       </c>
     </row>
     <row r="102">
@@ -3187,29 +5064,47 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="D104">
+        <v>1593382759.216121</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
         <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
+      <c r="D105">
+        <v>136601490.66413957</v>
+      </c>
+      <c r="H105">
+        <v>542263589.5753145</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
+      <c r="B106">
+        <v>-1133378</v>
+      </c>
+      <c r="C106">
+        <v>-1133377.8648344602</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C107">
-        <v>441264304</v>
-      </c>
-      <c r="D107">
-        <v>441264304</v>
-      </c>
-      <c r="E107">
-        <v>385271101</v>
+      <c r="I107">
+        <v>542263588.791561</v>
+      </c>
+      <c r="J107">
+        <v>473454317.4966085</v>
       </c>
     </row>
     <row r="108">
@@ -3222,13 +5117,28 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>1928237910</v>
+        <v>965153</v>
       </c>
       <c r="C109">
-        <v>735342121</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>430064308</v>
+        <v>2443504009.582102</v>
+      </c>
+      <c r="E109">
+        <v>2369584848.903933</v>
+      </c>
+      <c r="F109">
+        <v>1314793995</v>
+      </c>
+      <c r="G109">
+        <v>737189100.1627419</v>
+      </c>
+      <c r="H109">
+        <v>903651741.6641654</v>
+      </c>
+      <c r="I109">
+        <v>528500068.90029174</v>
       </c>
     </row>
     <row r="110">
@@ -3236,16 +5146,31 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-1274619212</v>
+        <v>-47219528</v>
       </c>
       <c r="C110">
-        <v>-304911700</v>
+        <v>-24167268.788105745</v>
       </c>
       <c r="D110">
-        <v>-34735834</v>
+        <v>-1685789137.4268374</v>
       </c>
       <c r="E110">
-        <v>-342971360</v>
+        <v>-1566361887.8217525</v>
+      </c>
+      <c r="F110">
+        <v>-685405814</v>
+      </c>
+      <c r="G110">
+        <v>-412369994.64462316</v>
+      </c>
+      <c r="H110">
+        <v>-374701763.1926338</v>
+      </c>
+      <c r="I110">
+        <v>-42686385.08431882</v>
+      </c>
+      <c r="J110">
+        <v>-421472751.90952784</v>
       </c>
     </row>
     <row r="111">
@@ -3288,10 +5213,22 @@
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
       <c r="B118">
-        <v>-285021055</v>
+        <v>-79276527</v>
       </c>
       <c r="C118">
-        <v>-163594617</v>
+        <v>-66562504.79549699</v>
+      </c>
+      <c r="D118">
+        <v>-447138288.2288247</v>
+      </c>
+      <c r="E118">
+        <v>-350258425.0854265</v>
+      </c>
+      <c r="F118">
+        <v>-120078881</v>
+      </c>
+      <c r="H118">
+        <v>-201039157.61621806</v>
       </c>
     </row>
     <row r="119">
@@ -3318,17 +5255,14 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B123">
-        <v>3097</v>
-      </c>
-      <c r="C123">
-        <v>16551</v>
-      </c>
-      <c r="D123">
-        <v>17411</v>
-      </c>
       <c r="E123">
-        <v>-31829</v>
+        <v>3805.860386312745</v>
+      </c>
+      <c r="I123">
+        <v>21396.136643878333</v>
+      </c>
+      <c r="J123">
+        <v>-39114.21706036434</v>
       </c>
     </row>
     <row r="124">
@@ -3340,6 +5274,24 @@
       <c r="A125" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
+      <c r="B125">
+        <v>-9293761</v>
+      </c>
+      <c r="C125">
+        <v>-7685078.6054428285</v>
+      </c>
+      <c r="D125">
+        <v>8827621.68316984</v>
+      </c>
+      <c r="F125">
+        <v>-1124163</v>
+      </c>
+      <c r="G125">
+        <v>10783448.319543079</v>
+      </c>
+      <c r="H125">
+        <v>-95721702.27713037</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -3351,44 +5303,100 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>97751831</v>
+        <v>-9293761</v>
       </c>
       <c r="C127">
-        <v>-77893060</v>
+        <v>-7685078.6054428285</v>
       </c>
       <c r="D127">
-        <v>-79651948</v>
+        <v>8827621.68316984</v>
       </c>
       <c r="E127">
-        <v>81354499</v>
+        <v>120125870.61428419</v>
+      </c>
+      <c r="F127">
+        <v>-1124163</v>
+      </c>
+      <c r="G127">
+        <v>10783448.319543079</v>
+      </c>
+      <c r="H127">
+        <v>-95721702.27713037</v>
+      </c>
+      <c r="I127">
+        <v>-97883175.19723691</v>
+      </c>
+      <c r="J127">
+        <v>99975416.52968028</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B128">
+        <v>13081335</v>
+      </c>
+      <c r="C128">
+        <v>13081337.458101658</v>
+      </c>
+      <c r="D128">
+        <v>4253715.072125606</v>
+      </c>
+      <c r="F128">
+        <v>4253712</v>
+      </c>
+      <c r="G128">
+        <v>4253708.869184379</v>
+      </c>
+      <c r="H128">
+        <v>99975417.34925596</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B129">
+        <v>1814718</v>
+      </c>
+      <c r="C129">
+        <v>5396258.85265883</v>
+      </c>
+      <c r="D129">
+        <v>13081336.755295444</v>
+      </c>
+      <c r="F129">
+        <v>2521648</v>
+      </c>
+      <c r="G129">
+        <v>15037157.188727457</v>
+      </c>
+      <c r="H129">
+        <v>4253715.072125606</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:J129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3396,15 +5404,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -3417,30 +5440,102 @@
       <c r="A3" t="str">
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
+      <c r="B3">
+        <v>-246615003.7423048</v>
+      </c>
       <c r="C3">
-        <v>133052256</v>
+        <v>-786835915.2576952</v>
+      </c>
+      <c r="D3">
+        <v>-493735194.01239854</v>
+      </c>
+      <c r="E3">
+        <v>179548686.8228895</v>
+      </c>
+      <c r="F3">
+        <v>-197363069.6963281</v>
+      </c>
+      <c r="G3">
+        <v>-311227942.3036719</v>
+      </c>
+      <c r="H3">
+        <v>163506074.32594717</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
+      <c r="B4">
+        <v>-47795348.050680965</v>
+      </c>
       <c r="C4">
-        <v>-72093838</v>
+        <v>197914115.05068097</v>
+      </c>
+      <c r="D4">
+        <v>-28508678.345012873</v>
+      </c>
+      <c r="E4">
+        <v>152794834.47794324</v>
+      </c>
+      <c r="F4">
+        <v>-20533294.145039484</v>
+      </c>
+      <c r="G4">
+        <v>-35817009.854960516</v>
+      </c>
+      <c r="H4">
+        <v>-88595118.21642745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B5">
+        <v>48940204.583266556</v>
+      </c>
       <c r="C5">
-        <v>88223223</v>
+        <v>-202943373.58326656</v>
+      </c>
+      <c r="D5">
+        <v>-1618062.9710437953</v>
+      </c>
+      <c r="E5">
+        <v>44179062.62783247</v>
+      </c>
+      <c r="F5">
+        <v>22382673.24277298</v>
+      </c>
+      <c r="G5">
+        <v>14249724.75722702</v>
+      </c>
+      <c r="H5">
+        <v>108416296.53150801</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B6">
+        <v>400684.07154605683</v>
+      </c>
+      <c r="C6">
+        <v>400684.92845394317</v>
+      </c>
+      <c r="D6">
+        <v>514284.5531475436</v>
+      </c>
+      <c r="E6">
+        <v>153458.5066583117</v>
+      </c>
+      <c r="F6">
+        <v>161501.51476954744</v>
+      </c>
+      <c r="G6">
+        <v>161502.48523045256</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -3451,8 +5546,26 @@
       <c r="A8" t="str">
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B8">
+        <v>-1847628.9805236454</v>
+      </c>
       <c r="C8">
-        <v>1378537</v>
+        <v>1841949.9805236454</v>
+      </c>
+      <c r="D8">
+        <v>-1475462.4979882194</v>
+      </c>
+      <c r="E8">
+        <v>-3809681.8071881263</v>
+      </c>
+      <c r="F8">
+        <v>3038393.6066634953</v>
+      </c>
+      <c r="G8">
+        <v>-5112097.606663495</v>
+      </c>
+      <c r="H8">
+        <v>1694065.84801714</v>
       </c>
     </row>
     <row r="9">
@@ -3474,8 +5587,26 @@
       <c r="A12" t="str">
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B12">
+        <v>-670394.9859907827</v>
+      </c>
       <c r="C12">
-        <v>-733170</v>
+        <v>-1916320.0140092173</v>
+      </c>
+      <c r="D12">
+        <v>-7710163.939624741</v>
+      </c>
+      <c r="E12">
+        <v>2113538.858842012</v>
+      </c>
+      <c r="F12">
+        <v>-575388.2829722194</v>
+      </c>
+      <c r="G12">
+        <v>-809515.7170277806</v>
+      </c>
+      <c r="H12">
+        <v>-900982.3188844388</v>
       </c>
     </row>
     <row r="13">
@@ -3517,22 +5648,40 @@
       <c r="A20" t="str">
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B20">
+        <v>-57467944.76930179</v>
+      </c>
       <c r="C20">
-        <v>87577856</v>
+        <v>-10142166.230698213</v>
+      </c>
+      <c r="D20">
+        <v>-140891245.56623068</v>
+      </c>
+      <c r="E20">
+        <v>50929568.69485809</v>
+      </c>
+      <c r="F20">
+        <v>19758166.404312156</v>
+      </c>
+      <c r="G20">
+        <v>20009835.595687844</v>
+      </c>
+      <c r="H20">
+        <v>107623213.00237532</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="C21">
-        <v>-12706677</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="D22">
+        <v>4538914.743131019</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -3553,6 +5702,12 @@
       <c r="A26" t="str">
         <v xml:space="preserve">    Yatırım ya da Finansman Faaliyetlerinden Kaynaklanan Nakit Akışlarına Neden Olan Diğer Kalemlere İlişkin Düzeltmeler</v>
       </c>
+      <c r="C26">
+        <v>-193127522.24753672</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -3563,6 +5718,18 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
+      <c r="B28">
+        <v>-218089646.01064456</v>
+      </c>
+      <c r="C28">
+        <v>-865778960.9893554</v>
+      </c>
+      <c r="F28">
+        <v>-147892259.52936837</v>
+      </c>
+      <c r="G28">
+        <v>-255082388.47063163</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -3578,8 +5745,26 @@
       <c r="A31" t="str">
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B31">
+        <v>255524266.51153427</v>
+      </c>
       <c r="C31">
-        <v>-480465377</v>
+        <v>87440469.48846574</v>
+      </c>
+      <c r="D31">
+        <v>182247448.87729606</v>
+      </c>
+      <c r="E31">
+        <v>-284154142.9192242</v>
+      </c>
+      <c r="F31">
+        <v>114269366.27690251</v>
+      </c>
+      <c r="G31">
+        <v>-11592647.276902508</v>
+      </c>
+      <c r="H31">
+        <v>-590437244.2579441</v>
       </c>
     </row>
     <row r="32">
@@ -3591,17 +5776,32 @@
       <c r="A33" t="str">
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B33">
+        <v>93821.84478139179</v>
+      </c>
       <c r="C33">
-        <v>-103449116</v>
+        <v>2200922.155218608</v>
+      </c>
+      <c r="D33">
+        <v>1058672.0090889335</v>
+      </c>
+      <c r="E33">
+        <v>1220025.7468980849</v>
+      </c>
+      <c r="F33">
+        <v>195149766.92789274</v>
+      </c>
+      <c r="G33">
+        <v>23164200.072107255</v>
+      </c>
+      <c r="H33">
+        <v>-127127184.87758861</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="C34">
-        <v>-397057176</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -3617,8 +5817,26 @@
       <c r="A37" t="str">
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B37">
+        <v>-108034664.18708253</v>
+      </c>
       <c r="C37">
-        <v>46663011</v>
+        <v>-829697868.8129175</v>
+      </c>
+      <c r="D37">
+        <v>-2488957845.1374807</v>
+      </c>
+      <c r="E37">
+        <v>-116839839.7533069</v>
+      </c>
+      <c r="F37">
+        <v>4475544.01012741</v>
+      </c>
+      <c r="G37">
+        <v>-93796142.01012741</v>
+      </c>
+      <c r="H37">
+        <v>57343527.633227766</v>
       </c>
     </row>
     <row r="38">
@@ -3630,16 +5848,52 @@
       <c r="A39" t="str">
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
+      <c r="B39">
+        <v>-417723676.5371191</v>
+      </c>
       <c r="C39">
-        <v>938288448</v>
+        <v>-156552719.4628809</v>
+      </c>
+      <c r="D39">
+        <v>1460212060.5335732</v>
+      </c>
+      <c r="E39">
+        <v>191762525.36238778</v>
+      </c>
+      <c r="F39">
+        <v>-659442670.9576722</v>
+      </c>
+      <c r="G39">
+        <v>-560717881.0423278</v>
+      </c>
+      <c r="H39">
+        <v>1153049671.9884975</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B40">
+        <v>-42358215.59126808</v>
+      </c>
       <c r="C40">
-        <v>1870872</v>
+        <v>-97534002.40873192</v>
+      </c>
+      <c r="D40">
+        <v>588723089.2673014</v>
+      </c>
+      <c r="E40">
+        <v>1954676.1772085</v>
+      </c>
+      <c r="F40">
+        <v>-3317520.0890336595</v>
+      </c>
+      <c r="G40">
+        <v>16981795.08903366</v>
+      </c>
+      <c r="H40">
+        <v>2299089.15346219</v>
       </c>
     </row>
     <row r="41">
@@ -3651,21 +5905,63 @@
       <c r="A42" t="str">
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
+      <c r="B42">
+        <v>-1927959.3460692987</v>
+      </c>
       <c r="C42">
-        <v>1521526</v>
+        <v>-113181.65393070133</v>
+      </c>
+      <c r="D42">
+        <v>820543.5258317124</v>
+      </c>
+      <c r="E42">
+        <v>-1683450.2894256986</v>
+      </c>
+      <c r="F42">
+        <v>-31599.73554467084</v>
+      </c>
+      <c r="G42">
+        <v>1032929.7355446708</v>
+      </c>
+      <c r="H42">
+        <v>1869781.8722527348</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B43">
+        <v>83950392.73093612</v>
+      </c>
+      <c r="C43">
+        <v>79885917.26906388</v>
+      </c>
+      <c r="F43">
+        <v>365378902.3503235</v>
+      </c>
+      <c r="G43">
+        <v>336768568.6496765</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
       <c r="C44">
         <v>0</v>
+      </c>
+      <c r="F44">
+        <v>-385127.3201482386</v>
+      </c>
+      <c r="G44">
+        <v>385127.3201482386</v>
+      </c>
+      <c r="H44">
+        <v>-0.3910828286316246</v>
       </c>
     </row>
     <row r="45">
@@ -3687,14 +5983,44 @@
       <c r="A48" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B48">
+        <v>-113752270.43635724</v>
+      </c>
       <c r="C48">
-        <v>122156077</v>
+        <v>48591502.436357245</v>
+      </c>
+      <c r="D48">
+        <v>-114637553.62343673</v>
+      </c>
+      <c r="E48">
+        <v>86057632.80610709</v>
+      </c>
+      <c r="F48">
+        <v>-239434357.99221566</v>
+      </c>
+      <c r="G48">
+        <v>32691660.99221567</v>
+      </c>
+      <c r="H48">
+        <v>150115910.13289753</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>-216944789.47805893</v>
+      </c>
+      <c r="C49">
+        <v>-870808219.5219411</v>
+      </c>
+      <c r="F49">
+        <v>-146042880.4316349</v>
+      </c>
+      <c r="G49">
+        <v>-276649673.5683651</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -3720,8 +6046,26 @@
       <c r="A54" t="str">
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
+      <c r="B54">
+        <v>12853.85100110172</v>
+      </c>
       <c r="C54">
-        <v>101285</v>
+        <v>-329716.8510011017</v>
+      </c>
+      <c r="D54">
+        <v>-0.33376999080064707</v>
+      </c>
+      <c r="E54">
+        <v>-4995.647430224373</v>
+      </c>
+      <c r="F54">
+        <v>-150588.22611295304</v>
+      </c>
+      <c r="G54">
+        <v>-83795.77388704698</v>
+      </c>
+      <c r="H54">
+        <v>124468.08379701199</v>
       </c>
     </row>
     <row r="55">
@@ -3784,6 +6128,18 @@
       <c r="A67" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
+      <c r="B67">
+        <v>278613676.8810884</v>
+      </c>
+      <c r="C67">
+        <v>872207761.1189116</v>
+      </c>
+      <c r="F67">
+        <v>576356.8614155599</v>
+      </c>
+      <c r="G67">
+        <v>-2418807.86141556</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -3824,21 +6180,69 @@
       <c r="A75" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
+      <c r="B75">
+        <v>-1559808272.882563</v>
+      </c>
+      <c r="C75">
+        <v>2708042995.882563</v>
+      </c>
+      <c r="F75">
+        <v>969.505040421647</v>
+      </c>
+      <c r="G75">
+        <v>1716.494959578353</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
+      <c r="C76">
+        <v>-1837751554.7776606</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="B77">
+        <v>-0.29281255044043064</v>
+      </c>
+      <c r="C77">
+        <v>1797171.2928125504</v>
+      </c>
+      <c r="D77">
+        <v>2049813.217858769</v>
+      </c>
+      <c r="E77">
+        <v>8114858.977310661</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
+      <c r="B78">
+        <v>0.29281255044043064</v>
+      </c>
+      <c r="C78">
+        <v>-1797171.2928125504</v>
+      </c>
+      <c r="D78">
+        <v>-5622148.698681518</v>
+      </c>
+      <c r="E78">
+        <v>-9207470.45573797</v>
+      </c>
+      <c r="F78">
+        <v>-7818370.926597081</v>
+      </c>
+      <c r="G78">
+        <v>-3230040.073402919</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -3919,6 +6323,18 @@
       <c r="A94" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
+      <c r="B94">
+        <v>670394.9859907827</v>
+      </c>
+      <c r="C94">
+        <v>1916320.0140092173</v>
+      </c>
+      <c r="F94">
+        <v>575388.2829722194</v>
+      </c>
+      <c r="G94">
+        <v>809515.7170277806</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -3938,9 +6354,6 @@
     <row r="98">
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
-      </c>
-      <c r="C98">
-        <v>733170</v>
       </c>
     </row>
     <row r="99">
@@ -3953,8 +6366,26 @@
       <c r="A101" t="str">
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
+      <c r="B101">
+        <v>-34801128.5515628</v>
+      </c>
       <c r="C101">
-        <v>-128492668</v>
+        <v>-91863151.4484372</v>
+      </c>
+      <c r="D101">
+        <v>1587596297.8099468</v>
+      </c>
+      <c r="E101">
+        <v>-56344764.00324601</v>
+      </c>
+      <c r="F101">
+        <v>184490194.48188132</v>
+      </c>
+      <c r="G101">
+        <v>324819105.5181187</v>
+      </c>
+      <c r="H101">
+        <v>-157902859.71913373</v>
       </c>
     </row>
     <row r="102">
@@ -3981,14 +6412,17 @@
       <c r="A106" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Almasıyla İlgili Nakit Çıkışları</v>
       </c>
+      <c r="B106">
+        <v>-0.1351655398029834</v>
+      </c>
+      <c r="C106">
+        <v>-1133377.8648344602</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C107">
-        <v>0</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -3999,16 +6433,52 @@
       <c r="A109" t="str">
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="B109">
+        <v>965153</v>
+      </c>
       <c r="C109">
-        <v>305277813</v>
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>73919160.67816877</v>
+      </c>
+      <c r="E109">
+        <v>1054790853.903933</v>
+      </c>
+      <c r="F109">
+        <v>577604894.8372581</v>
+      </c>
+      <c r="G109">
+        <v>737189100.1627419</v>
+      </c>
+      <c r="H109">
+        <v>375151672.76387364</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
+      <c r="B110">
+        <v>-23052259.211894255</v>
+      </c>
       <c r="C110">
-        <v>-270175866</v>
+        <v>-24167268.788105745</v>
+      </c>
+      <c r="D110">
+        <v>-119427249.6050849</v>
+      </c>
+      <c r="E110">
+        <v>-880956073.8217525</v>
+      </c>
+      <c r="F110">
+        <v>-273035819.35537684</v>
+      </c>
+      <c r="G110">
+        <v>-412369994.64462316</v>
+      </c>
+      <c r="H110">
+        <v>-332015378.108315</v>
       </c>
     </row>
     <row r="111">
@@ -4050,6 +6520,18 @@
       <c r="A118" t="str">
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
+      <c r="B118">
+        <v>-12714022.204503007</v>
+      </c>
+      <c r="C118">
+        <v>-66562504.79549699</v>
+      </c>
+      <c r="D118">
+        <v>-96879863.14339817</v>
+      </c>
+      <c r="E118">
+        <v>-230179544.0854265</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -4075,9 +6557,6 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="C123">
-        <v>-860</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -4088,6 +6567,18 @@
       <c r="A125" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
+      <c r="B125">
+        <v>-1608682.3945571715</v>
+      </c>
+      <c r="C125">
+        <v>-7685078.6054428285</v>
+      </c>
+      <c r="F125">
+        <v>-11907611.319543079</v>
+      </c>
+      <c r="G125">
+        <v>10783448.319543079</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -4098,36 +6589,83 @@
       <c r="A127" t="str">
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
+      <c r="B127">
+        <v>-1608682.3945571715</v>
+      </c>
       <c r="C127">
-        <v>1758888</v>
+        <v>-7685078.6054428285</v>
+      </c>
+      <c r="D127">
+        <v>-111298248.93111435</v>
+      </c>
+      <c r="E127">
+        <v>121250033.61428419</v>
+      </c>
+      <c r="F127">
+        <v>-11907611.319543079</v>
+      </c>
+      <c r="G127">
+        <v>10783448.319543079</v>
+      </c>
+      <c r="H127">
+        <v>2161472.920106545</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B128">
+        <v>-2.4581016581505537</v>
+      </c>
+      <c r="C128">
+        <v>13081337.458101658</v>
+      </c>
+      <c r="F128">
+        <v>3.1308156214654446</v>
+      </c>
+      <c r="G128">
+        <v>4253708.869184379</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B129">
+        <v>-3581540.8526588297</v>
+      </c>
+      <c r="C129">
+        <v>5396258.85265883</v>
+      </c>
+      <c r="F129">
+        <v>-12515509.188727457</v>
+      </c>
+      <c r="G129">
+        <v>15037157.188727457</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:J129"/>
   <cols>
     <col min="1" max="1" customWidth="1" width="40" level="2" outlineLevel="2"/>
     <col min="2" max="2" customWidth="1" width="20"/>
     <col min="3" max="3" customWidth="1" width="20"/>
     <col min="4" max="4" customWidth="1" width="20"/>
     <col min="5" max="5" customWidth="1" width="20"/>
+    <col min="6" max="6" customWidth="1" width="20"/>
+    <col min="7" max="7" customWidth="1" width="20"/>
+    <col min="8" max="8" customWidth="1" width="20"/>
+    <col min="9" max="9" customWidth="1" width="20"/>
+    <col min="10" max="10" customWidth="1" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4135,15 +6673,30 @@
         <v>Kalem</v>
       </c>
       <c r="B1" t="str">
+        <v>2026/6</v>
+      </c>
+      <c r="C1" t="str">
+        <v>2026/3</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2025/12</v>
+      </c>
+      <c r="E1" t="str">
         <v>2025/9</v>
       </c>
-      <c r="C1" t="str">
+      <c r="F1" t="str">
+        <v>2025/6</v>
+      </c>
+      <c r="G1" t="str">
+        <v>2025/3</v>
+      </c>
+      <c r="H1" t="str">
         <v>2024/12</v>
       </c>
-      <c r="D1" t="str">
+      <c r="I1" t="str">
         <v>2024/9</v>
       </c>
-      <c r="E1" t="str">
+      <c r="J1" t="str">
         <v>2023/12</v>
       </c>
     </row>
@@ -4157,13 +6710,22 @@
         <v xml:space="preserve">    İşletme Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B3">
-        <v>-134704303</v>
+        <v>-1347637426.189509</v>
       </c>
       <c r="C3">
-        <v>-763337695</v>
+        <v>-1298385492.1435323</v>
+      </c>
+      <c r="D3">
+        <v>-822777519.189509</v>
       </c>
       <c r="E3">
-        <v>36857861</v>
+        <v>-165536250.85116333</v>
+      </c>
+      <c r="H3">
+        <v>-938055115.599698</v>
+      </c>
+      <c r="J3">
+        <v>45294114.66067855</v>
       </c>
     </row>
     <row r="4">
@@ -4171,13 +6733,22 @@
         <v xml:space="preserve">    Dönem Karı (Zararı)</v>
       </c>
       <c r="B4">
-        <v>6387420</v>
+        <v>274404923.1329304</v>
       </c>
       <c r="C4">
-        <v>-300695370</v>
+        <v>301666977.03857183</v>
+      </c>
+      <c r="D4">
+        <v>67935852.13293037</v>
       </c>
       <c r="E4">
-        <v>134446780</v>
+        <v>7849412.261515796</v>
+      </c>
+      <c r="H4">
+        <v>-369520373.2662193</v>
+      </c>
+      <c r="J4">
+        <v>165219784.9755585</v>
       </c>
     </row>
     <row r="5">
@@ -4185,19 +6756,40 @@
         <v xml:space="preserve">    Dönem Net Karı (Zararı) Mutabakatı İle İlgili Düzeltmeler</v>
       </c>
       <c r="B5">
-        <v>153983148</v>
+        <v>-111442169.34321132</v>
       </c>
       <c r="C5">
-        <v>32320623</v>
+        <v>-137999700.6837049</v>
+      </c>
+      <c r="D5">
+        <v>79193397.65678868</v>
       </c>
       <c r="E5">
-        <v>46058431</v>
+        <v>189227757.1593405</v>
+      </c>
+      <c r="H5">
+        <v>39718366.007811904</v>
+      </c>
+      <c r="J5">
+        <v>56600567.645663194</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v xml:space="preserve">    Amortisman ve İtfa Gideri İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B6">
+        <v>1469112.0598058552</v>
+      </c>
+      <c r="C6">
+        <v>1229929.503029346</v>
+      </c>
+      <c r="D6">
+        <v>990747.0598058553</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -4209,10 +6801,19 @@
         <v xml:space="preserve">    Karşılıklar İle İlgili Düzeltmeler</v>
       </c>
       <c r="B8">
-        <v>-3409039</v>
+        <v>-5290823.305176346</v>
       </c>
       <c r="C8">
-        <v>1654686</v>
+        <v>-404800.7179892049</v>
+      </c>
+      <c r="D8">
+        <v>-7358848.305176346</v>
+      </c>
+      <c r="E8">
+        <v>-4189319.959170986</v>
+      </c>
+      <c r="H8">
+        <v>2033421.5276490026</v>
       </c>
     </row>
     <row r="9">
@@ -4235,13 +6836,22 @@
         <v xml:space="preserve">    Faiz (Gelirleri) ve Giderleri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B12">
-        <v>-140247</v>
+        <v>-8183340.080782728</v>
       </c>
       <c r="C12">
-        <v>-2334509</v>
+        <v>-8088333.377764165</v>
+      </c>
+      <c r="D12">
+        <v>-6981529.080782728</v>
       </c>
       <c r="E12">
-        <v>-2228726</v>
+        <v>-172347.4600424267</v>
+      </c>
+      <c r="H12">
+        <v>-2868845.6269753864</v>
+      </c>
+      <c r="J12">
+        <v>-2738850.498981356</v>
       </c>
     </row>
     <row r="13">
@@ -4273,6 +6883,15 @@
       <c r="A18" t="str">
         <v xml:space="preserve">    Gerçeğe Uygun Değer Kayıpları (Kazançları) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B18">
+        <v>58803576.7365213</v>
+      </c>
+      <c r="D18">
+        <v>143405609.7365213</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -4284,33 +6903,42 @@
         <v xml:space="preserve">    Vergi (Geliri) Gideri İle İlgili Düzeltmeler</v>
       </c>
       <c r="B20">
-        <v>161382554</v>
+        <v>-157571787.87137258</v>
       </c>
       <c r="C20">
-        <v>33000446</v>
+        <v>-80345676.69775866</v>
+      </c>
+      <c r="D20">
+        <v>-50193674.871372595</v>
       </c>
       <c r="E20">
-        <v>48287157</v>
+        <v>198320783.6972334</v>
+      </c>
+      <c r="H20">
+        <v>40553790.10713829</v>
+      </c>
+      <c r="J20">
+        <v>59339418.14464455</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v xml:space="preserve">    Nakit Dışı Kalemlere İlişkin Diğer Düzeltmeler</v>
       </c>
-      <c r="B21">
-        <v>-143372373</v>
-      </c>
-      <c r="C21">
-        <v>-39629662</v>
-      </c>
-      <c r="E21">
-        <v>17981922</v>
+      <c r="J21">
+        <v>22097734.778677963</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v xml:space="preserve">    Duran Varlıkların Elden Çıkarılmasından Kaynaklanan Kayıplar (Kazançlar) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="D22">
+        <v>-668906.8822067977</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -4341,6 +6969,18 @@
       <c r="A28" t="str">
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Değişimler</v>
       </c>
+      <c r="B28">
+        <v>-1542423327.4157214</v>
+      </c>
+      <c r="C28">
+        <v>-1472225940.9344451</v>
+      </c>
+      <c r="D28">
+        <v>-861529368.4157213</v>
+      </c>
+      <c r="H28">
+        <v>-559718246.6062034</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -4357,10 +6997,19 @@
         <v xml:space="preserve">    Ticari Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B31">
-        <v>-628141730</v>
+        <v>241058041.9580719</v>
       </c>
       <c r="C31">
-        <v>-529290590</v>
+        <v>99803141.72344011</v>
+      </c>
+      <c r="D31">
+        <v>770024.9580718696</v>
+      </c>
+      <c r="E31">
+        <v>-771914668.1771684</v>
+      </c>
+      <c r="H31">
+        <v>-650437871.9653971</v>
       </c>
     </row>
     <row r="32">
@@ -4373,24 +7022,27 @@
         <v xml:space="preserve">    Faaliyetlerle İlgili Diğer Alacaklardaki Azalış (Artış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B33">
-        <v>75195581</v>
+        <v>4573441.755987018</v>
       </c>
       <c r="C33">
-        <v>-199286781</v>
+        <v>199629386.83909836</v>
+      </c>
+      <c r="D33">
+        <v>220592664.75598702</v>
+      </c>
+      <c r="E33">
+        <v>92406807.86930947</v>
+      </c>
+      <c r="H33">
+        <v>-244900763.41818</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Varlıklardaki Azalış (Artış) İle İlgili Düzeltmeler</v>
       </c>
-      <c r="B34">
-        <v>381505151</v>
-      </c>
-      <c r="C34">
-        <v>319907867</v>
-      </c>
-      <c r="E34">
-        <v>4006694013</v>
+      <c r="J34">
+        <v>4923770753.681996</v>
       </c>
     </row>
     <row r="35">
@@ -4408,13 +7060,22 @@
         <v xml:space="preserve">    Stoklardaki Azalışlar (Artışlar) İle İlgili Düzeltmeler</v>
       </c>
       <c r="B37">
-        <v>-121099022</v>
+        <v>-3543530217.8907876</v>
       </c>
       <c r="C37">
-        <v>188079477</v>
+        <v>-3431020009.693578</v>
+      </c>
+      <c r="D37">
+        <v>-2695118282.8907876</v>
       </c>
       <c r="E37">
-        <v>-2892170272</v>
+        <v>-148816910.12007913</v>
+      </c>
+      <c r="H37">
+        <v>231128263.15849194</v>
+      </c>
+      <c r="J37">
+        <v>-3554147971.803732</v>
       </c>
     </row>
     <row r="38">
@@ -4427,13 +7088,22 @@
         <v xml:space="preserve">    Peşin Ödenmiş Giderlerdeki Azalış (Artış)</v>
       </c>
       <c r="B39">
-        <v>101434658</v>
+        <v>1077698189.8959608</v>
       </c>
       <c r="C39">
-        <v>-564137167</v>
+        <v>835979195.4754078</v>
+      </c>
+      <c r="D39">
+        <v>431814033.8959609</v>
       </c>
       <c r="E39">
-        <v>-674622924</v>
+        <v>124651645.35088527</v>
+      </c>
+      <c r="H39">
+        <v>-693260347.872679</v>
+      </c>
+      <c r="J39">
+        <v>-829034763.3677992</v>
       </c>
     </row>
     <row r="40">
@@ -4441,13 +7111,22 @@
         <v xml:space="preserve">    Ticari Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B40">
-        <v>14580716</v>
+        <v>450785547.44451</v>
       </c>
       <c r="C40">
-        <v>2230530</v>
+        <v>489826242.94674444</v>
+      </c>
+      <c r="D40">
+        <v>604342040.44451</v>
       </c>
       <c r="E40">
-        <v>636105</v>
+        <v>17918040.330670692</v>
+      </c>
+      <c r="H40">
+        <v>2741067.8860487156</v>
+      </c>
+      <c r="J40">
+        <v>781700.6202891407</v>
       </c>
     </row>
     <row r="41">
@@ -4460,29 +7139,59 @@
         <v xml:space="preserve">    Çalışanlara Sağlanan Faydalar Kapsamında Borçlardaki Artış (Azalış)</v>
       </c>
       <c r="B42">
-        <v>966454</v>
+        <v>-2904047.763593986</v>
       </c>
       <c r="C42">
-        <v>1749285</v>
+        <v>-1007688.1530693583</v>
+      </c>
+      <c r="D42">
+        <v>138423.2364060139</v>
       </c>
       <c r="E42">
-        <v>559094</v>
+        <v>1187661.5828270363</v>
+      </c>
+      <c r="H42">
+        <v>2149671.7514023003</v>
+      </c>
+      <c r="J42">
+        <v>687062.8694947168</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
         <v xml:space="preserve">    Müşteri Sözleşmelerinden Doğan Yükümlülüklerdeki Artış (Azalış) İle İlgili Düzeltmeler</v>
       </c>
+      <c r="B43">
+        <v>272943184.0014601</v>
+      </c>
+      <c r="C43">
+        <v>554371693.6208475</v>
+      </c>
+      <c r="D43">
+        <v>811254345.0014601</v>
+      </c>
+      <c r="H43">
+        <v>393130345.280793</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
         <v xml:space="preserve">    Faaliyetler ile İlgili Diğer Borçlardaki Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
       <c r="C44">
-        <v>-424494</v>
-      </c>
-      <c r="E44">
-        <v>424495</v>
+        <v>-385127.3201482386</v>
+      </c>
+      <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>-521655.1856670851</v>
+      </c>
+      <c r="J44">
+        <v>521656.02347039996</v>
       </c>
     </row>
     <row r="45">
@@ -4505,19 +7214,40 @@
         <v xml:space="preserve">    İşletme Sermayesinde Gerçekleşen Diğer Artış (Azalış) ile İlgili Düzeltmeler</v>
       </c>
       <c r="B48">
-        <v>23949205</v>
+        <v>-93740688.81732965</v>
       </c>
       <c r="C48">
-        <v>325703928</v>
+        <v>-219422776.37318808</v>
+      </c>
+      <c r="D48">
+        <v>-235322617.81732965</v>
       </c>
       <c r="E48">
-        <v>-602949919</v>
+        <v>29430845.939004615</v>
+      </c>
+      <c r="H48">
+        <v>400253043.75898373</v>
+      </c>
+      <c r="J48">
+        <v>-740956800.6627635</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
         <v xml:space="preserve">    Faaliyetlerden Elde Edilen Nakit Akışları</v>
       </c>
+      <c r="B49">
+        <v>-1379460573.6260023</v>
+      </c>
+      <c r="C49">
+        <v>-1308558664.5795782</v>
+      </c>
+      <c r="D49">
+        <v>-714400118.6260022</v>
+      </c>
+      <c r="H49">
+        <v>-889520253.864611</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -4544,13 +7274,22 @@
         <v xml:space="preserve">    Vergi İadeleri (Ödemeleri)</v>
       </c>
       <c r="B54">
-        <v>-93509</v>
+        <v>-321858.9812002152</v>
       </c>
       <c r="C54">
-        <v>134659</v>
+        <v>-485301.05831426993</v>
+      </c>
+      <c r="D54">
+        <v>-239379.98120021517</v>
       </c>
       <c r="E54">
-        <v>-199864</v>
+        <v>-114911.56363321238</v>
+      </c>
+      <c r="H54">
+        <v>165480.92994903057</v>
+      </c>
+      <c r="J54">
+        <v>-245610.1001775946</v>
       </c>
     </row>
     <row r="55">
@@ -4613,6 +7352,18 @@
       <c r="A67" t="str">
         <v xml:space="preserve">    Yatırım Faaliyetlerinden Kaynaklanan Nakit Akışları</v>
       </c>
+      <c r="B67">
+        <v>-55287870.11997056</v>
+      </c>
+      <c r="C67">
+        <v>-333325190.1396433</v>
+      </c>
+      <c r="D67">
+        <v>-1207951759.1199706</v>
+      </c>
+      <c r="H67">
+        <v>2889185.117895654</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -4653,21 +7404,54 @@
       <c r="A75" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Satılması Sonucu Elde Edilen Nakit Girişleri</v>
       </c>
+      <c r="B75">
+        <v>2192763126.3587074</v>
+      </c>
+      <c r="C75">
+        <v>3752572368.7463107</v>
+      </c>
+      <c r="D75">
+        <v>1044531089.3587073</v>
+      </c>
+      <c r="H75">
+        <v>20339.490920267403</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
         <v xml:space="preserve">    Başka İşletmelerin veya Fonların Paylarının veya Borçlanma Araçlarının Edinimi İçin Yapılan Nakit Çıkışları</v>
       </c>
+      <c r="C76">
+        <v>-4089320944.3778706</v>
+      </c>
+      <c r="D76">
+        <v>-2251569389.60021</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Satışından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="B77">
+        <v>11961843.19516943</v>
+      </c>
+      <c r="D77">
+        <v>17983042.19516943</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
         <v xml:space="preserve">    Maddi ve Maddi Olmayan Duran Varlıkların Alımından Kaynaklanan Nakit Çıkışları</v>
       </c>
+      <c r="B78">
+        <v>-16626790.15441949</v>
+      </c>
+      <c r="C78">
+        <v>-24445161.37382912</v>
+      </c>
+      <c r="D78">
+        <v>-25878030.15441949</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4748,6 +7532,18 @@
       <c r="A94" t="str">
         <v xml:space="preserve">    Alınan Faiz</v>
       </c>
+      <c r="B94">
+        <v>8183340.080782728</v>
+      </c>
+      <c r="C94">
+        <v>8088333.377764165</v>
+      </c>
+      <c r="D94">
+        <v>6981529.080782728</v>
+      </c>
+      <c r="H94">
+        <v>2868845.6269753864</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4768,14 +7564,8 @@
       <c r="A98" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B98">
-        <v>1860129</v>
-      </c>
-      <c r="C98">
-        <v>2334509</v>
-      </c>
-      <c r="E98">
-        <v>2228726</v>
+      <c r="J98">
+        <v>2738850.498981356</v>
       </c>
     </row>
     <row r="99">
@@ -4789,13 +7579,22 @@
         <v xml:space="preserve">    Finansman Faaliyetlerinden Nakit Akışları</v>
       </c>
       <c r="B101">
-        <v>240104975</v>
+        <v>1404587253.8067007</v>
       </c>
       <c r="C101">
-        <v>708100108</v>
+        <v>1623878576.8401449</v>
+      </c>
+      <c r="D101">
+        <v>2040560833.8067007</v>
       </c>
       <c r="E101">
-        <v>42299741</v>
+        <v>295061676.27762026</v>
+      </c>
+      <c r="H101">
+        <v>870174410.430628</v>
+      </c>
+      <c r="J101">
+        <v>51981565.58708075</v>
       </c>
     </row>
     <row r="102">
@@ -4812,11 +7611,23 @@
       <c r="A104" t="str">
         <v xml:space="preserve">    Pay ve Diğer Özkaynağa Dayalı Araçların İhracından Kaynaklanan Nakit Girişleri</v>
       </c>
+      <c r="D104">
+        <v>1593382759.216121</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
         <v xml:space="preserve">    Sermaye Avanslarından Nakit Girişleri</v>
       </c>
+      <c r="D105">
+        <v>136601490.66413957</v>
+      </c>
+      <c r="H105">
+        <v>542263589.5753145</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -4827,11 +7638,8 @@
       <c r="A107" t="str">
         <v xml:space="preserve">    İşletmenin Kendi Paylarını ve Diğer Özkaynağa Dayalı Araçlarını Satmasından Kaynaklanan Nakit Girişleri</v>
       </c>
-      <c r="C107">
-        <v>441264304</v>
-      </c>
-      <c r="E107">
-        <v>385271101</v>
+      <c r="J107">
+        <v>473454317.4966085</v>
       </c>
     </row>
     <row r="108">
@@ -4844,10 +7652,19 @@
         <v xml:space="preserve">    Borçlanmadan Kaynaklanan Nakit Girişleri</v>
       </c>
       <c r="B109">
-        <v>2233515723</v>
+        <v>1129675167.5821018</v>
       </c>
       <c r="C109">
-        <v>735342121</v>
+        <v>1706314909.41936</v>
+      </c>
+      <c r="D109">
+        <v>2443504009.582102</v>
+      </c>
+      <c r="E109">
+        <v>2744736521.6678066</v>
+      </c>
+      <c r="H109">
+        <v>903651741.6641654</v>
       </c>
     </row>
     <row r="110">
@@ -4855,13 +7672,22 @@
         <v xml:space="preserve">    Borç Ödemelerine İlişkin Nakit Çıkışları</v>
       </c>
       <c r="B110">
-        <v>-1544795078</v>
+        <v>-1047602851.4268374</v>
       </c>
       <c r="C110">
-        <v>-304911700</v>
+        <v>-1297586411.57032</v>
+      </c>
+      <c r="D110">
+        <v>-1685789137.4268374</v>
       </c>
       <c r="E110">
-        <v>-342971360</v>
+        <v>-1898377265.9300675</v>
+      </c>
+      <c r="H110">
+        <v>-374701763.1926338</v>
+      </c>
+      <c r="J110">
+        <v>-421472751.90952784</v>
       </c>
     </row>
     <row r="111">
@@ -4903,8 +7729,14 @@
       <c r="A118" t="str">
         <v xml:space="preserve">    Ödenen Faiz</v>
       </c>
-      <c r="C118">
-        <v>-163594617</v>
+      <c r="B118">
+        <v>-406335934.2288247</v>
+      </c>
+      <c r="D118">
+        <v>-447138288.2288247</v>
+      </c>
+      <c r="H118">
+        <v>-201039157.61621806</v>
       </c>
     </row>
     <row r="119">
@@ -4931,14 +7763,8 @@
       <c r="A123" t="str">
         <v xml:space="preserve">    Diğer Nakit Girişleri (Çıkışları)</v>
       </c>
-      <c r="B123">
-        <v>2237</v>
-      </c>
-      <c r="C123">
-        <v>16551</v>
-      </c>
-      <c r="E123">
-        <v>-31829</v>
+      <c r="J123">
+        <v>-39114.21706036434</v>
       </c>
     </row>
     <row r="124">
@@ -4950,6 +7776,18 @@
       <c r="A125" t="str">
         <v xml:space="preserve">    Yabancı Para Çevrim Farklarının Etkisinden Önce Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
+      <c r="B125">
+        <v>658023.6831698399</v>
+      </c>
+      <c r="C125">
+        <v>-9640905.241816066</v>
+      </c>
+      <c r="D125">
+        <v>8827621.68316984</v>
+      </c>
+      <c r="H125">
+        <v>-95721702.27713037</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -4961,28 +7799,61 @@
         <v xml:space="preserve">    Nakit ve Nakit Benzerlerindeki Net Artış (Azalış)</v>
       </c>
       <c r="B127">
-        <v>99510719</v>
+        <v>658023.6831698399</v>
       </c>
       <c r="C127">
-        <v>-77893060</v>
+        <v>-9640905.241816066</v>
+      </c>
+      <c r="D127">
+        <v>8827621.68316984</v>
       </c>
       <c r="E127">
-        <v>81354499</v>
+        <v>122287343.53439073</v>
+      </c>
+      <c r="H127">
+        <v>-95721702.27713037</v>
+      </c>
+      <c r="J127">
+        <v>99975416.52968028</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
         <v xml:space="preserve">    Dönem Başı Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B128">
+        <v>13081338.072125606</v>
+      </c>
+      <c r="C128">
+        <v>13081343.661042886</v>
+      </c>
+      <c r="D128">
+        <v>4253715.072125606</v>
+      </c>
+      <c r="H128">
+        <v>99975417.34925596</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
         <v xml:space="preserve">    Dönem Sonu Nakit ve Nakit Benzerleri</v>
       </c>
+      <c r="B129">
+        <v>12374406.755295444</v>
+      </c>
+      <c r="C129">
+        <v>3440438.419226817</v>
+      </c>
+      <c r="D129">
+        <v>13081336.755295444</v>
+      </c>
+      <c r="H129">
+        <v>4253715.072125606</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J129"/>
   </ignoredErrors>
 </worksheet>
 </file>